--- a/resultados/rodada04/simulacoes_v03.xlsx
+++ b/resultados/rodada04/simulacoes_v03.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -471,40 +471,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B_RS1bi: R$ 1000 mi por tecnologia do RS. B_TWh: 1 TWh de cada tecnologia ao R$/MWh da v03 (SOL-RS latente: R$/MWh do SOL-RB); 'evitadas' = CO₂e do carvão − CO₂e da tecnologia, por TWh.</t>
+          <t>B_RS1bi: R$ 1000 mi por tecnologia do RS. B_TWh: 1 TWh de cada tecnologia; na linha v03 ao R$/MWh da v03, nas linhas das variantes ao R$/MWh de cada variante (SOL-RS latente: R$/MWh do SOL-RB da mesma versão); 'evitadas' = CO₂e do carvão − CO₂e da tecnologia, por TWh.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LIMITAÇÃO: HID, EOL e SOL têm a mesma estrutura de insumos não energéticos (não há dado de custo por tecnologia); as diferenças entre elas vêm do VBP (R$/MWh) e, no SOL-RS, da coluna latente (espelho do SOL-RB), e não de tecnologia.</t>
+          <t>B_TWh, versão 'v03 (SOL-RS com a TUST/MWh do RS)': HIPÓTESE ALTERNATIVA para o SOL-RS latente. Na v03 a coluna latente é o espelho do SOL-RB e paga a TUST por MWh do RB (cerca de 21 R$/MWh); nesta linha as linhas S38_TRA da coluna são multiplicadas para que pague a TUST por MWh das fontes do RS (cerca de 35 R$/MWh).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>robustez: A2 (R1, F1, E1) e B por TWh nas variantes _P2, _E2, _E3, _gas4dist, _rap_ons, _k060 e _eta005 (faixa mín–máx de CO₂e total, IC e % no RB); robustez_detalhe: os valores de cada variante.</t>
+          <t>LIMITAÇÃO: HID, EOL e SOL têm a mesma estrutura de insumos não energéticos (não há dado de custo por tecnologia); as diferenças entre elas vêm do VBP (R$/MWh) e, no SOL-RS, da coluna latente (espelho do SOL-RB), e não de tecnologia.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tabela1_artigo a tabela4_artigo: as tabelas do artigo refeitas com o A2. ORDEM E RÓTULOS INFERIDOS (o artigo não foi recebido): 1 = impactos totais; 2 = top-10 da cesta R1; 3 = RS × RB; 4 = diretas × indiretas.</t>
+          <t>robustez: A2 (R1, F1, E1) e B por TWh nas variantes _P2, _E2, _E3, _gas4dist, _rap_ons, _k060 e _eta005 (faixa mín–máx de CO₂e total, IC e % no RB); robustez_detalhe: os valores de cada variante.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emissões diretas = e · ΔY (setores chocados); indiretas = total − diretas (eq. 12–14 do modelo).</t>
+          <t>tabela1_artigo a tabela4_artigo: as tabelas do artigo refeitas com o A2. ORDEM E RÓTULOS INFERIDOS (o artigo não foi recebido): 1 = impactos totais; 2 = top-10 da cesta R1; 3 = RS × RB; 4 = diretas × indiretas.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Emissões diretas = e · ΔY (setores chocados); indiretas = total − diretas (eq. 12–14 do modelo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Gerado por scripts/rodada04_simulacoes.py.</t>
         </is>
@@ -529,7 +536,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -708,16 +715,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>130486.0827273468</v>
@@ -726,10 +733,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="4">
@@ -762,16 +769,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>130486.0827273468</v>
@@ -780,10 +787,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="5">
@@ -891,7 +898,7 @@
         <v>70.18171450297378</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>54.22965902303684</v>
+        <v>54.22965902303685</v>
       </c>
     </row>
     <row r="7">
@@ -1023,7 +1030,7 @@
         <v>1382.391803829019</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>732.2477510848989</v>
+        <v>732.2477510848988</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>340253.7952674468</v>
@@ -1032,7 +1039,7 @@
         <v>257572.8787420347</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>82680.91652541213</v>
+        <v>82680.91652541215</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>160.9039207068543</v>
@@ -1053,7 +1060,7 @@
         <v>47.58821359374465</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>36.7101495878202</v>
+        <v>36.71014958782021</v>
       </c>
     </row>
     <row r="10">
@@ -1130,7 +1137,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1216,19 +1223,19 @@
         <v>283632.3099730055</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
     </row>
     <row r="3">
@@ -1355,7 +1362,7 @@
         <v>1384.75301923389</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>108263.4417851559</v>
@@ -2075,7 +2082,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -2147,16 +2154,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>205.0628482296878</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.7362804720336</v>
+        <v>189.7362804720337</v>
       </c>
     </row>
     <row r="3">
@@ -2172,7 +2179,7 @@
         <v>484.8638356007575</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>26.16628508207372</v>
+        <v>26.16628508207373</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>43862.25968469489</v>
@@ -2262,10 +2269,10 @@
         <v>1384.75301923389</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>27.73287882213273</v>
+        <v>27.73287882213274</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>46081.34365313985</v>
@@ -2296,7 +2303,7 @@
         <v>438.6033393816223</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24.36902394342163</v>
+        <v>24.36902394342162</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>88602.82237278513</v>
@@ -2311,7 +2318,7 @@
         <v>65.08996705461921</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>91.74125300737539</v>
+        <v>91.74125300737541</v>
       </c>
     </row>
     <row r="8">
@@ -2393,7 +2400,7 @@
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2446,10 +2453,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>34.04721157468089</v>
+        <v>34.04721157468087</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
     </row>
     <row r="3">
@@ -7997,7 +8004,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>36.00362942355253</v>
+        <v>36.00362942355252</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>15.69327076389992</v>
@@ -8099,28 +8106,28 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24.99359038000249</v>
+        <v>24.99359038000248</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46685.27860369316</v>
+        <v>46685.2786036932</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>12.18140298811914</v>
+        <v>12.18140298811915</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5.41832541361802</v>
+        <v>5.418325413618017</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.08931469505017961</v>
+        <v>0.08931469505017968</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>9.24943216905152</v>
+        <v>9.249432169051527</v>
       </c>
     </row>
     <row r="5">
@@ -8168,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5.76511390215683</v>
+        <v>5.765113902156829</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>3.082116251747031</v>
@@ -8219,7 +8226,7 @@
         <v>1055.33598848684</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9767.235609922602</v>
+        <v>9767.235609922604</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -8231,10 +8238,10 @@
         <v>2.006399228119421</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.009744632593869861</v>
+        <v>0.009744632593869864</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.387675429321748</v>
+        <v>1.387675429321749</v>
       </c>
     </row>
     <row r="7">
@@ -8396,7 +8403,7 @@
         <v>3292.433258480532</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.8636562228026171</v>
+        <v>0.863656222802617</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>12.41022190322594</v>
@@ -8453,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.7282756988867258</v>
+        <v>0.7282756988867257</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>0.3491421765887651</v>
@@ -8498,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.615850636287813</v>
+        <v>5.615850636287814</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>454.0827600827758</v>
@@ -8510,16 +8517,16 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.6653772043830464</v>
+        <v>0.6653772043830465</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>36.11811598081736</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.004833734554475374</v>
+        <v>0.004833734554475375</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.5008500189351007</v>
+        <v>0.5008500189351008</v>
       </c>
     </row>
     <row r="12">
@@ -8726,28 +8733,28 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>7.95636445557311</v>
+        <v>7.956364455573106</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14861.6139431551</v>
+        <v>14861.61394315511</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7.340081779878862</v>
+        <v>7.340081779878865</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1.72484909427545</v>
+        <v>1.724849094275448</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.02843210016061445</v>
+        <v>0.02843210016061447</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2.944429040613439</v>
+        <v>2.944429040613441</v>
       </c>
     </row>
     <row r="16">
@@ -9353,28 +9360,28 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.976462547351007</v>
+        <v>8.976462547351003</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16767.04501142814</v>
+        <v>16767.04501142815</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4.927805433661328</v>
+        <v>4.927805433661331</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1.945994729257361</v>
+        <v>1.945994729257359</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0320774247659705</v>
+        <v>0.03207742476597051</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.321938952643837</v>
+        <v>3.32193895264384</v>
       </c>
     </row>
     <row r="27">
@@ -9923,28 +9930,28 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>4.653194447694811</v>
+        <v>4.653194447694809</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8691.655575887244</v>
+        <v>8691.655575887249</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4.157519603651973</v>
+        <v>4.157519603651976</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1.008759499820552</v>
+        <v>1.008759499820551</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.01662820894422491</v>
+        <v>0.01662820894422492</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1.722017755712136</v>
+        <v>1.722017755712137</v>
       </c>
     </row>
     <row r="37">
@@ -10493,28 +10500,28 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4.317018212099999</v>
+        <v>4.317018212099997</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8063.715332806289</v>
+        <v>8063.715332806293</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4.985323033436063</v>
+        <v>4.985323033436067</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.9358803250768057</v>
+        <v>0.935880325076805</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.01542688182360075</v>
+        <v>0.01542688182360076</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>1.597608287496269</v>
+        <v>1.59760828749627</v>
       </c>
     </row>
     <row r="47">
@@ -11006,28 +11013,28 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>11.58272651460288</v>
+        <v>11.58272651460287</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21635.25952466879</v>
+        <v>21635.2595246688</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>7.478541967393432</v>
+        <v>7.478541967393437</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2.511003040334447</v>
+        <v>2.511003040334445</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.04139091946265955</v>
+        <v>0.04139091946265958</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>4.286444708448613</v>
+        <v>4.286444708448616</v>
       </c>
     </row>
     <row r="56">
@@ -11240,7 +11247,7 @@
         <v>1055.33598848684</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4526.4092574687</v>
+        <v>4526.409257468701</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -11252,10 +11259,10 @@
         <v>0.9298213335932588</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.00451593438973807</v>
+        <v>0.004515934389738072</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.6430874774089317</v>
+        <v>0.6430874774089318</v>
       </c>
     </row>
     <row r="60">
@@ -11291,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>9.704544904710737</v>
+        <v>9.704544904710739</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>454.0827600827758</v>
@@ -11303,16 +11310,16 @@
         <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1.523228347956821</v>
+        <v>1.523228347956822</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>62.41438761645669</v>
+        <v>62.41438761645671</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.008352998873981112</v>
+        <v>0.008352998873981114</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0.8655004938831151</v>
+        <v>0.8655004938831152</v>
       </c>
     </row>
     <row r="61">
@@ -11348,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>3.568490417265904</v>
+        <v>3.568490417265905</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>986.3644347220352</v>
@@ -11369,7 +11376,7 @@
         <v>0.1067348812758426</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0.009619550811217431</v>
+        <v>0.009619550811217433</v>
       </c>
     </row>
     <row r="62">
@@ -11588,7 +11595,7 @@
         <v>22597.23628208163</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>8.07039497745772</v>
+        <v>8.070394977457719</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>9.863644452992409</v>
@@ -11633,28 +11640,28 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>8.577880810307825</v>
+        <v>8.577880810307821</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16022.53815357817</v>
+        <v>16022.53815357818</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4.369978752573584</v>
+        <v>4.369978752573585</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.859586753356746</v>
+        <v>1.859586753356745</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.03065309133666592</v>
+        <v>0.03065309133666594</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>3.174434945234268</v>
+        <v>3.17443494523427</v>
       </c>
     </row>
     <row r="67">
@@ -11816,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2.285951454635434</v>
+        <v>2.285951454635433</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>195.6125849243836</v>
@@ -12203,28 +12210,28 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>12.67393420126537</v>
+        <v>12.67393420126536</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>23673.51549717165</v>
+        <v>23673.51549717166</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6.707784725039928</v>
+        <v>6.707784725039931</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.747564424684786</v>
+        <v>2.747564424684784</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.04529035448935549</v>
+        <v>0.04529035448935552</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>4.690270302398006</v>
+        <v>4.690270302398009</v>
       </c>
     </row>
     <row r="77">
@@ -12665,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>36.00362942355253</v>
+        <v>36.00362942355252</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>15.69327076389992</v>
@@ -12767,28 +12774,28 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24.99359038000249</v>
+        <v>24.99359038000248</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46685.27860369316</v>
+        <v>46685.2786036932</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>12.18140298811914</v>
+        <v>12.18140298811915</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5.41832541361802</v>
+        <v>5.418325413618017</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.08931469505017961</v>
+        <v>0.08931469505017968</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>9.24943216905152</v>
+        <v>9.249432169051527</v>
       </c>
     </row>
     <row r="5">
@@ -12836,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5.76511390215683</v>
+        <v>5.765113902156829</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>3.082116251747031</v>
@@ -12887,7 +12894,7 @@
         <v>1055.33598848684</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9767.235609922602</v>
+        <v>9767.235609922604</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -12899,10 +12906,10 @@
         <v>2.006399228119421</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.009744632593869861</v>
+        <v>0.009744632593869864</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.387675429321748</v>
+        <v>1.387675429321749</v>
       </c>
     </row>
     <row r="7">
@@ -13064,7 +13071,7 @@
         <v>3292.433258480532</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.8636562228026171</v>
+        <v>0.863656222802617</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>12.41022190322594</v>
@@ -13121,7 +13128,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.7282756988867258</v>
+        <v>0.7282756988867257</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>0.3491421765887651</v>
@@ -13166,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.615850636287813</v>
+        <v>5.615850636287814</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>454.0827600827758</v>
@@ -13178,16 +13185,16 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.6653772043830464</v>
+        <v>0.6653772043830465</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>36.11811598081736</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.004833734554475374</v>
+        <v>0.004833734554475375</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.5008500189351007</v>
+        <v>0.5008500189351008</v>
       </c>
     </row>
     <row r="12">
@@ -15674,28 +15681,28 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>9.302495471878597</v>
+        <v>9.302495471878595</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4224.102819528158</v>
+        <v>4224.102819528157</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3.278543312891315</v>
+        <v>3.278543312891314</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>59.82862296822668</v>
+        <v>59.82862296822667</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.008006942619648008</v>
+        <v>0.008006942619648006</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.8296436880155127</v>
+        <v>0.8296436880155125</v>
       </c>
     </row>
     <row r="56">
@@ -15737,7 +15744,7 @@
         <v>986.3644347220352</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3371.717956238566</v>
+        <v>3371.717956238567</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -17339,7 +17346,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>7.139560026488312</v>
+        <v>7.139560026488311</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>96.10190632373236</v>
@@ -17396,7 +17403,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>6.848682643624906</v>
+        <v>6.848682643624905</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>151.9045802714326</v>
@@ -17453,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>5.311380556859563</v>
+        <v>5.311380556859562</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>43.12823920326056</v>
@@ -17681,13 +17688,13 @@
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2.623303773785914</v>
+        <v>2.623303773785913</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>53.34849592324981</v>
+        <v>53.34849592324982</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1.630944636946807</v>
+        <v>1.630944636946808</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>0.06796544961110619</v>
@@ -19892,7 +19899,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>0.50686194642656</v>
+        <v>0.5068619464265601</v>
       </c>
       <c r="I129" s="2" t="n">
         <v>5809.446984300834</v>
@@ -19904,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>2.725691480597453</v>
+        <v>2.725691480597454</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>19.14239088355535</v>
+        <v>19.14239088355536</v>
       </c>
       <c r="N129" s="2" t="n">
         <v>0.1377731150560019</v>
@@ -20861,7 +20868,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>3.392074351829577</v>
+        <v>3.392074351829578</v>
       </c>
       <c r="I146" s="2" t="n">
         <v>986.3644347220352</v>
@@ -20873,16 +20880,16 @@
         <v>0</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2.611004854092368</v>
+        <v>2.611004854092369</v>
       </c>
       <c r="M146" s="2" t="n">
         <v>21.97901142244593</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.1014582108640653</v>
+        <v>0.1014582108640654</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>0.009143987447737799</v>
+        <v>0.009143987447737801</v>
       </c>
     </row>
     <row r="147">
@@ -25319,10 +25326,10 @@
         <v>159.9554704585595</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0009669352521332689</v>
+        <v>0.0009669352521332692</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>3.996132838347893</v>
+        <v>3.996132838347894</v>
       </c>
     </row>
     <row r="3">
@@ -25421,22 +25428,22 @@
         <v>454.0827600827758</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2144.363810137887</v>
+        <v>2144.363810137886</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8.037543452282973</v>
+        <v>8.03754345228297</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30.37197231808397</v>
+        <v>30.37197231808396</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.004064720655957362</v>
+        <v>0.004064720655957361</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.4211682281182061</v>
+        <v>0.421168228118206</v>
       </c>
     </row>
     <row r="5">
@@ -25472,7 +25479,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5.374561794723369</v>
+        <v>5.37456179472337</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>243.170196149393</v>
@@ -25490,10 +25497,10 @@
         <v>4.424441722843972</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.005079877943695796</v>
+        <v>0.005079877943695797</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.6403871081274405</v>
+        <v>0.6403871081274406</v>
       </c>
     </row>
     <row r="6">
@@ -25544,13 +25551,13 @@
         <v>4.611897691072537</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.082769367341061</v>
+        <v>8.082769367341063</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0.037311201267215</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.003362696356872876</v>
+        <v>0.003362696356872877</v>
       </c>
     </row>
     <row r="7">
@@ -25604,7 +25611,7 @@
         <v>22.18030384050008</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.6780856136329969</v>
+        <v>0.678085613632997</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.02825748499450295</v>
@@ -25757,13 +25764,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6039611171274233</v>
+        <v>0.6039611171274234</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>1263.027928569804</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>762.8197587021541</v>
+        <v>762.8197587021542</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -25772,7 +25779,7 @@
         <v>2.85921489993544</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.879758251581248</v>
+        <v>4.879758251581249</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0.02890588982709608</v>
@@ -25928,7 +25935,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5.926190421182046</v>
+        <v>5.926190421182047</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>445.9483457946769</v>
@@ -25943,7 +25950,7 @@
         <v>11.20860628882232</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>61.67909022986574</v>
+        <v>61.67909022986576</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0.0002365414491422552</v>
@@ -25985,7 +25992,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4.322729787410322</v>
+        <v>4.322729787410323</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>454.0827600827758</v>
@@ -25997,13 +26004,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.325006042019455</v>
+        <v>8.325006042019456</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27.80146159988047</v>
+        <v>27.80146159988048</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.00372070585496861</v>
+        <v>0.003720705854968611</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0.38552294854247</v>
@@ -26054,16 +26061,16 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.034535536307087</v>
+        <v>5.034535536307088</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4.018583798970036</v>
+        <v>4.018583798970037</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.004613896279813436</v>
+        <v>0.004613896279813437</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.581643836442268</v>
+        <v>0.5816438364422681</v>
       </c>
     </row>
     <row r="16">
@@ -26099,28 +26106,28 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.130747033926362</v>
+        <v>1.130747033926363</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1115.328658932394</v>
+        <v>1115.328658932395</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.730361341706963</v>
+        <v>4.730361341706966</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7.326697293990509</v>
+        <v>7.326697293990513</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0338210661391131</v>
+        <v>0.03382106613911312</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.003048145651410202</v>
+        <v>0.003048145651410203</v>
       </c>
     </row>
     <row r="17">
@@ -26156,13 +26163,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.1445449537538843</v>
+        <v>0.1445449537538844</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>5809.446984300834</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>839.7262456814069</v>
+        <v>839.726245681407</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -26171,10 +26178,10 @@
         <v>3.561469113499061</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5.458953911433933</v>
+        <v>5.458953911433934</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.03928961068136491</v>
+        <v>0.03928961068136492</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>0.002961511063028327</v>
@@ -26213,13 +26220,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.5863855418958264</v>
+        <v>0.5863855418958266</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1263.027928569804</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>740.6213163239676</v>
+        <v>740.6213163239678</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -26228,13 +26235,13 @@
         <v>3.14114267173635</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4.737754808262599</v>
+        <v>4.737754808262601</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.02806471375319794</v>
+        <v>0.02806471375319795</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.001580714771696628</v>
+        <v>0.001580714771696629</v>
       </c>
     </row>
     <row r="19">
@@ -26270,28 +26277,28 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.9474898320172374</v>
+        <v>0.9474898320172379</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>712.0842822082119</v>
+        <v>712.0842822082124</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3.020110649554334</v>
+        <v>3.020110649554336</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15.2376841899528</v>
+        <v>15.23768418995281</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4658391746385113</v>
+        <v>0.4658391746385116</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.01941265707831973</v>
+        <v>0.01941265707831974</v>
       </c>
     </row>
     <row r="20">
@@ -26333,7 +26340,7 @@
         <v>2963.345789569951</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>641.1203333734376</v>
+        <v>641.1203333734377</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -26342,13 +26349,13 @@
         <v>2.719136477022796</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4.965379308987135</v>
+        <v>4.965379308987136</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0.1098302330147003</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.004432692898328075</v>
+        <v>0.004432692898328076</v>
       </c>
     </row>
     <row r="21">
@@ -26384,13 +26391,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.928555455307872</v>
+        <v>1.928555455307873</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>283.3622708942781</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>546.4798533615871</v>
+        <v>546.4798533615874</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -26399,13 +26406,13 @@
         <v>2.317744775641092</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2.338284105754659</v>
+        <v>2.33828410575466</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>6.213967214396945e-05</v>
+        <v>6.213967214396949e-05</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.1324825699072097</v>
+        <v>0.1324825699072098</v>
       </c>
     </row>
     <row r="22">
@@ -26498,25 +26505,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>7.491431438322408</v>
+        <v>7.491431438322406</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3340.791457554115</v>
+        <v>3340.791457554114</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>12.44605845009004</v>
+        <v>12.44605845009003</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>77.96993393657721</v>
+        <v>77.96993393657718</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0002990173994809264</v>
+        <v>0.0002990173994809263</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>1.403340952941476</v>
@@ -26675,19 +26682,19 @@
         <v>986.3644347220352</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1239.286935329045</v>
+        <v>1239.286935329046</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4.61694117382315</v>
+        <v>4.616941173823151</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8.140990696181406</v>
+        <v>8.140990696181408</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.03757995911736277</v>
+        <v>0.03757995911736278</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>0.003386918333461098</v>
@@ -26789,7 +26796,7 @@
         <v>5809.446984300834</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>964.3027651454557</v>
+        <v>964.3027651454559</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -26798,13 +26805,13 @@
         <v>3.592492596760472</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6.268810077891196</v>
+        <v>6.268810077891198</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0451183709171608</v>
+        <v>0.04511837091716081</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.003400862271215189</v>
+        <v>0.00340086227121519</v>
       </c>
     </row>
     <row r="29">
@@ -27365,16 +27372,16 @@
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3.14081249081112</v>
+        <v>3.140812490811121</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>4.399422207562695</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.005051152040677771</v>
+        <v>0.005051152040677772</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.6367658207331456</v>
+        <v>0.6367658207331457</v>
       </c>
     </row>
     <row r="39">
@@ -27473,22 +27480,22 @@
         <v>57.55493465680681</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1055.624311310083</v>
+        <v>1055.624311310082</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2.551295856210708</v>
+        <v>2.551295856210707</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.930282585062349</v>
+        <v>0.9302825850623485</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.006223234229095389</v>
+        <v>0.006223234229095386</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.441353825149903</v>
+        <v>0.4413538251499028</v>
       </c>
     </row>
     <row r="41">
@@ -27695,13 +27702,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>7.457756190916336</v>
+        <v>7.457756190916335</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3325.774036679151</v>
+        <v>3325.77403667915</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -27710,7 +27717,7 @@
         <v>0.05930298013707058</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>77.61944593743223</v>
+        <v>77.61944593743222</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0.0002976732658545102</v>
@@ -28835,13 +28842,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>25.63941984229257</v>
+        <v>25.63941984229256</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1867.890042762577</v>
+        <v>1867.890042762578</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>47891.61702562752</v>
+        <v>47891.61702562755</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -28850,13 +28857,13 @@
         <v>12.35349351868922</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5.558333877195524</v>
+        <v>5.55833387719552</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.09162256921318951</v>
+        <v>0.09162256921318956</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>9.488435678087445</v>
+        <v>9.488435678087452</v>
       </c>
     </row>
     <row r="65">
@@ -28961,13 +28968,13 @@
         <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2.5845295436053</v>
+        <v>2.584529543605301</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>2.058244189764962</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.009996431984538787</v>
+        <v>0.009996431984538793</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>1.423532689632339</v>
@@ -29234,7 +29241,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>6.910986840927687</v>
+        <v>6.910986840927688</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>243.170196149393</v>
@@ -29246,16 +29253,16 @@
         <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0.433491615561104</v>
+        <v>0.4334916155611041</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5.689256109222936</v>
+        <v>5.689256109222937</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.006532061768620416</v>
+        <v>0.006532061768620417</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>0.8234544594339845</v>
+        <v>0.8234544594339847</v>
       </c>
     </row>
     <row r="72">
@@ -29354,7 +29361,7 @@
         <v>445.9483457946769</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>583.7845746243119</v>
+        <v>583.7845746243117</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -29405,28 +29412,28 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.8373185396161046</v>
+        <v>0.8373185396161043</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>380.2119135373599</v>
+        <v>380.2119135373597</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>8.037543452282973</v>
+        <v>8.03754345228297</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5.385180284412598</v>
+        <v>5.385180284412597</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0007207056989536703</v>
+        <v>0.00072070569895367</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>0.07467631060406003</v>
+        <v>0.07467631060406001</v>
       </c>
     </row>
     <row r="75">
@@ -29633,7 +29640,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.02924246575773172</v>
+        <v>0.02924246575773171</v>
       </c>
       <c r="I78" s="2" t="n">
         <v>5809.446984300834</v>
@@ -29690,13 +29697,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2.904499289924766</v>
+        <v>2.904499289924765</v>
       </c>
       <c r="I79" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>167.1682668423617</v>
+        <v>167.1682668423616</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -29705,13 +29712,13 @@
         <v>3.533877189927379</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0.1473191984613394</v>
+        <v>0.1473191984613393</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0009855090197201299</v>
+        <v>0.0009855090197201297</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>0.06989262488942766</v>
+        <v>0.06989262488942764</v>
       </c>
     </row>
     <row r="80">
@@ -29804,7 +29811,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.0418361574233286</v>
+        <v>0.04183615742332859</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>2963.345789569951</v>
@@ -29819,13 +29826,13 @@
         <v>2.620787044465586</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>0.9601674951107558</v>
+        <v>0.9601674951107556</v>
       </c>
       <c r="N81" s="2" t="n">
         <v>0.02123813975908856</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>0.0008571606259927586</v>
+        <v>0.0008571606259927585</v>
       </c>
     </row>
     <row r="82">
@@ -29873,7 +29880,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>37.6329227325412</v>
+        <v>37.63292273254119</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>30.67703510358005</v>
@@ -29975,7 +29982,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.841473278894439</v>
+        <v>0.8414732788944391</v>
       </c>
       <c r="I84" s="2" t="n">
         <v>454.0827600827758</v>
@@ -29990,13 +29997,13 @@
         <v>8.325006042019455</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5.411901321855313</v>
+        <v>5.411901321855314</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0007242818102349696</v>
+        <v>0.0007242818102349697</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>0.07504685130768525</v>
+        <v>0.07504685130768526</v>
       </c>
     </row>
     <row r="85">
@@ -30032,25 +30039,25 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.9502543168985896</v>
+        <v>0.9502543168985899</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>231.0735286320374</v>
+        <v>231.0735286320375</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>5.034535536307088</v>
+        <v>5.034535536307087</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.7822674680429675</v>
+        <v>0.7822674680429678</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0008981524689239001</v>
+        <v>0.0008981524689239003</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>0.1132242287327958</v>
@@ -30089,28 +30096,28 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.2201140161500129</v>
+        <v>0.220114016150013</v>
       </c>
       <c r="I86" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>217.1126371142044</v>
+        <v>217.1126371142045</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4.730361341706963</v>
+        <v>4.730361341706965</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1.426233028350979</v>
+        <v>1.42623302835098</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.006583692439594941</v>
+        <v>0.006583692439594944</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>0.0005933595764672069</v>
+        <v>0.0005933595764672072</v>
       </c>
     </row>
     <row r="87">
@@ -30164,10 +30171,10 @@
         <v>1.062653478958227</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.007648212854484368</v>
+        <v>0.00764821285448437</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>0.0005764950730777781</v>
+        <v>0.0005764950730777783</v>
       </c>
     </row>
     <row r="88">
@@ -30218,13 +30225,13 @@
         <v>3.14114267173635</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>0.9222630766136758</v>
+        <v>0.9222630766136761</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.005463146637552175</v>
+        <v>0.005463146637552177</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>0.0003077058496254738</v>
+        <v>0.0003077058496254739</v>
       </c>
     </row>
     <row r="89">
@@ -30260,28 +30267,28 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>0.1844407156766391</v>
+        <v>0.1844407156766392</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>138.6160887372764</v>
+        <v>138.6160887372765</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>3.020110649554334</v>
+        <v>3.020110649554335</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2.966205316700828</v>
+        <v>2.96620531670083</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.09068140665701498</v>
+        <v>0.09068140665701503</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>0.003778915871938693</v>
+        <v>0.003778915871938696</v>
       </c>
     </row>
     <row r="90">
@@ -30317,13 +30324,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0.04211525744486909</v>
+        <v>0.0421152574448691</v>
       </c>
       <c r="I90" s="2" t="n">
         <v>2963.345789569951</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>124.8020708259073</v>
+        <v>124.8020708259074</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -30332,13 +30339,13 @@
         <v>2.719136477022796</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>0.9665730252806575</v>
+        <v>0.9665730252806577</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.02137982498137755</v>
+        <v>0.02137982498137756</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>0.0008628789702172891</v>
+        <v>0.0008628789702172892</v>
       </c>
     </row>
     <row r="91">
@@ -30374,13 +30381,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.3754173779804735</v>
+        <v>0.3754173779804738</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>283.3622708942781</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>106.3791207577225</v>
+        <v>106.3791207577226</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -30389,13 +30396,13 @@
         <v>2.317744775641092</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0.4551761711284025</v>
+        <v>0.4551761711284028</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.209626237122187e-05</v>
+        <v>1.209626237122188e-05</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>0.02578938494394481</v>
+        <v>0.02578938494394483</v>
       </c>
     </row>
     <row r="92">
@@ -30494,7 +30501,7 @@
         <v>445.9483457946769</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>569.3322896928743</v>
+        <v>569.3322896928742</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -30503,13 +30510,13 @@
         <v>12.44605845009003</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>13.28751033379778</v>
+        <v>13.28751033379777</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>5.095806274274966e-05</v>
+        <v>5.095806274274965e-05</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>0.2391551008523282</v>
+        <v>0.2391551008523281</v>
       </c>
     </row>
     <row r="94">
@@ -30665,7 +30672,7 @@
         <v>986.3644347220352</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>211.1972798786772</v>
+        <v>211.1972798786773</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -30674,13 +30681,13 @@
         <v>4.61694117382315</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1.387374498622163</v>
+        <v>1.387374498622164</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0.006404315995981675</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>0.0005771931574573435</v>
+        <v>0.0005771931574573436</v>
       </c>
     </row>
     <row r="97">
@@ -30788,13 +30795,13 @@
         <v>3.592492596760472</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1.068320498493057</v>
+        <v>1.068320498493058</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.007688999971367849</v>
+        <v>0.00768899997136785</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>0.0005795694608302826</v>
+        <v>0.0005795694608302827</v>
       </c>
     </row>
     <row r="99">
@@ -31349,7 +31356,7 @@
         <v>243.170196149393</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>274.1815729464534</v>
+        <v>274.1815729464535</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -31358,7 +31365,7 @@
         <v>3.140812490811121</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>0.9282037891687911</v>
+        <v>0.9282037891687913</v>
       </c>
       <c r="N108" s="2" t="n">
         <v>0.00106570777766343</v>
@@ -31457,28 +31464,28 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>3.86967518644115</v>
+        <v>3.869675186441148</v>
       </c>
       <c r="I110" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>222.7189024986871</v>
+        <v>222.718902498687</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2.551295856210708</v>
+        <v>2.551295856210707</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>0.1962739150082597</v>
+        <v>0.1962739150082596</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>0.00131299732551276</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>0.09311820360502238</v>
+        <v>0.09311820360502235</v>
       </c>
     </row>
     <row r="111">
@@ -31691,19 +31698,19 @@
         <v>445.9483457946769</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>855.1788826320892</v>
+        <v>855.1788826320891</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0.0593029801370706</v>
+        <v>0.05930298013707059</v>
       </c>
       <c r="M114" s="2" t="n">
         <v>19.95881569680403</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>7.654275007122606e-05</v>
+        <v>7.654275007122605e-05</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>0.3592285131640556</v>
@@ -33628,7 +33635,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>34.21293454407457</v>
+        <v>34.21293454407456</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
@@ -33727,7 +33734,7 @@
         <v>137984.0624287731</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>36.00362942355253</v>
+        <v>36.00362942355252</v>
       </c>
     </row>
     <row r="34">
@@ -33758,7 +33765,7 @@
         <v>2791.119704026462</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.7282756988867258</v>
+        <v>0.7282756988867257</v>
       </c>
     </row>
     <row r="35">
@@ -33913,7 +33920,7 @@
         <v>3309.966135976186</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.8636562228026171</v>
+        <v>0.863656222802617</v>
       </c>
     </row>
     <row r="40">
@@ -34037,7 +34044,7 @@
         <v>27.75678691452548</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.007242467372454307</v>
+        <v>0.007242467372454306</v>
       </c>
     </row>
     <row r="44">
@@ -34068,7 +34075,7 @@
         <v>22094.82347531904</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5.76511390215683</v>
+        <v>5.765113902156829</v>
       </c>
     </row>
     <row r="45">
@@ -34093,13 +34100,13 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>24.99359038000249</v>
+        <v>24.99359038000248</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>46685.27860369316</v>
+        <v>46685.2786036932</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.18140298811914</v>
+        <v>12.18140298811915</v>
       </c>
     </row>
     <row r="46">
@@ -34127,7 +34134,7 @@
         <v>9.255095738682277</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>9767.235609922602</v>
+        <v>9767.235609922604</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>2.548525715233982</v>
@@ -34186,10 +34193,10 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>66.59251495416571</v>
+        <v>66.59251495416569</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>87.19069513370007</v>
+        <v>87.19069513370006</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0.0227503192870272</v>
@@ -34223,7 +34230,7 @@
         <v>656.2737306456557</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.171238879205889</v>
+        <v>0.1712388792058889</v>
       </c>
     </row>
     <row r="50">
@@ -34248,10 +34255,10 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5742136338365785</v>
+        <v>0.5742136338365786</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>125.2256120123902</v>
+        <v>125.2256120123903</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0.0326746179948063</v>
@@ -34285,7 +34292,7 @@
         <v>350893.2051467203</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="52">
@@ -34341,7 +34348,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.38407298442176</v>
+        <v>10.38407298442175</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0</v>
@@ -34651,7 +34658,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>32.7738444367795</v>
+        <v>32.77384443677951</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -34806,13 +34813,13 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>7.95636445557311</v>
+        <v>7.956364455573106</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>14861.6139431551</v>
+        <v>14861.61394315511</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>7.340081779878862</v>
+        <v>7.340081779878865</v>
       </c>
     </row>
     <row r="69">
@@ -34840,10 +34847,10 @@
         <v>2.946231959818591</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>3109.264617626673</v>
+        <v>3109.264617626674</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.535651286324453</v>
+        <v>1.535651286324454</v>
       </c>
     </row>
     <row r="70">
@@ -34899,13 +34906,13 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.98709713094634</v>
+        <v>20.98709713094633</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>27.4787577694755</v>
+        <v>27.47875776947549</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.01357163024210626</v>
+        <v>0.01357163024210625</v>
       </c>
     </row>
     <row r="72">
@@ -34961,13 +34968,13 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>2.159856914009871</v>
+        <v>2.159856914009872</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>471.0257436922063</v>
+        <v>471.0257436922064</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.2326374169288278</v>
+        <v>0.2326374169288279</v>
       </c>
     </row>
     <row r="74">
@@ -34992,13 +34999,13 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>448.1476485551723</v>
+        <v>448.1476485551724</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>109799.9015322432</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>54.22965902303684</v>
+        <v>54.22965902303685</v>
       </c>
     </row>
     <row r="75">
@@ -35054,7 +35061,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.03001306786095</v>
+        <v>12.03001306786094</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>0</v>
@@ -35519,13 +35526,13 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8.976462547351007</v>
+        <v>8.976462547351003</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>16767.04501142814</v>
+        <v>16767.04501142815</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>4.927805433661328</v>
+        <v>4.927805433661331</v>
       </c>
     </row>
     <row r="92">
@@ -35553,10 +35560,10 @@
         <v>3.32397302697657</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>3507.908360127912</v>
+        <v>3507.908360127913</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.03096817990542</v>
+        <v>1.030968179905421</v>
       </c>
     </row>
     <row r="93">
@@ -35615,10 +35622,10 @@
         <v>23.80921073828109</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>31.17379838085878</v>
+        <v>31.17379838085877</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.009161925249461361</v>
+        <v>0.009161925249461359</v>
       </c>
     </row>
     <row r="95">
@@ -35708,10 +35715,10 @@
         <v>509.7680781255566</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>124907.6772209152</v>
+        <v>124907.6772209153</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>36.7101495878202</v>
+        <v>36.71014958782021</v>
       </c>
     </row>
     <row r="98">
@@ -35767,7 +35774,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>5.841324809305753</v>
+        <v>5.841324809305751</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>0</v>
@@ -36232,13 +36239,13 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>4.653194447694811</v>
+        <v>4.653194447694809</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>8691.655575887244</v>
+        <v>8691.655575887249</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>4.157519603651973</v>
+        <v>4.157519603651976</v>
       </c>
     </row>
     <row r="115">
@@ -36269,7 +36276,7 @@
         <v>1818.420075643985</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.8698132416956058</v>
+        <v>0.8698132416956059</v>
       </c>
     </row>
     <row r="116">
@@ -36325,13 +36332,13 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12.17735833017105</v>
+        <v>12.17735833017104</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>15.94401921042552</v>
+        <v>15.94401921042551</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.007626576070529708</v>
+        <v>0.007626576070529706</v>
       </c>
     </row>
     <row r="118">
@@ -36421,7 +36428,7 @@
         <v>258.0243571357376</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>63274.63803697247</v>
+        <v>63274.63803697248</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30.26644875143274</v>
@@ -36480,7 +36487,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>5.281653826686584</v>
+        <v>5.281653826686583</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>0</v>
@@ -36945,13 +36952,13 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>4.317018212099999</v>
+        <v>4.317018212099997</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>8063.715332806289</v>
+        <v>8063.715332806293</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>4.985323033436063</v>
+        <v>4.985323033436067</v>
       </c>
     </row>
     <row r="138">
@@ -36982,7 +36989,7 @@
         <v>1687.045893320082</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.043001693799297</v>
+        <v>1.043001693799298</v>
       </c>
     </row>
     <row r="139">
@@ -37044,7 +37051,7 @@
         <v>14.71688123550027</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.009098585946504294</v>
+        <v>0.009098585946504293</v>
       </c>
     </row>
     <row r="141">
@@ -37134,7 +37141,7 @@
         <v>237.6714088800179</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>58275.26686067449</v>
+        <v>58275.2668606745</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>36.02818529297566</v>
@@ -37193,7 +37200,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>15.48895194220916</v>
+        <v>15.48895194220915</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>0</v>
@@ -37658,13 +37665,13 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>11.58272651460288</v>
+        <v>11.58272651460287</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>21635.25952466879</v>
+        <v>21635.2595246688</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>7.478541967393432</v>
+        <v>7.478541967393437</v>
       </c>
     </row>
     <row r="161">
@@ -37692,7 +37699,7 @@
         <v>4.289069364495707</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>4526.4092574687</v>
+        <v>4526.409257468701</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>1.564619160448737</v>
@@ -37751,10 +37758,10 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>30.70792307031993</v>
+        <v>30.70792307031992</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>40.20639797815433</v>
+        <v>40.20639797815432</v>
       </c>
       <c r="G163" s="2" t="n">
         <v>0.0138979259432735</v>
@@ -38129,7 +38136,7 @@
         <v>17.92952736590399</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.004890090002075577</v>
+        <v>0.004890090002075576</v>
       </c>
     </row>
     <row r="176">
@@ -38191,7 +38198,7 @@
         <v>1118.644798360781</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.3050986025845025</v>
+        <v>0.3050986025845024</v>
       </c>
     </row>
     <row r="178">
@@ -38371,13 +38378,13 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>8.577880810307825</v>
+        <v>8.577880810307821</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>16022.53815357817</v>
+        <v>16022.53815357818</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>4.369978752573584</v>
+        <v>4.369978752573585</v>
       </c>
     </row>
     <row r="184">
@@ -38405,7 +38412,7 @@
         <v>3.176378700593736</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>3352.146755799635</v>
+        <v>3352.146755799636</v>
       </c>
       <c r="G184" s="2" t="n">
         <v>0.9142627689784274</v>
@@ -38467,10 +38474,10 @@
         <v>22.7408046562554</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>29.77491640379259</v>
+        <v>29.77491640379258</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.008120795269579102</v>
+        <v>0.0081207952695791</v>
       </c>
     </row>
     <row r="187">
@@ -38501,7 +38508,7 @@
         <v>1105.037213459804</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.301387276930531</v>
+        <v>0.3013872769305309</v>
       </c>
     </row>
     <row r="188">
@@ -38532,7 +38539,7 @@
         <v>160.6037437995222</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.04380298185346804</v>
+        <v>0.04380298185346803</v>
       </c>
     </row>
     <row r="189">
@@ -38619,7 +38626,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>17.14992687789759</v>
+        <v>17.14992687789758</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>0</v>
@@ -39084,13 +39091,13 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>12.67393420126537</v>
+        <v>12.67393420126536</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>23673.51549717165</v>
+        <v>23673.51549717166</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>6.707784725039928</v>
+        <v>6.707784725039931</v>
       </c>
     </row>
     <row r="207">
@@ -39118,10 +39125,10 @@
         <v>4.693142227069619</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>4952.841891313847</v>
+        <v>4952.841891313848</v>
       </c>
       <c r="G207" s="2" t="n">
-        <v>1.403365595957309</v>
+        <v>1.40336559595731</v>
       </c>
     </row>
     <row r="208">
@@ -39177,13 +39184,13 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>33.68514111378493</v>
+        <v>33.68514111378492</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>44.10451942548179</v>
+        <v>44.10451942548178</v>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.01249681830072171</v>
+        <v>0.0124968183007217</v>
       </c>
     </row>
     <row r="210">
@@ -39239,13 +39246,13 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.7080950152047863</v>
+        <v>0.7080950152047866</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>154.4227207729068</v>
+        <v>154.4227207729069</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.04375498720176837</v>
+        <v>0.04375498720176838</v>
       </c>
     </row>
     <row r="212">
@@ -39273,10 +39280,10 @@
         <v>722.9000854610034</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>177070.5834747881</v>
+        <v>177070.5834747882</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>50.17215779498385</v>
+        <v>50.17215779498386</v>
       </c>
     </row>
     <row r="213">
@@ -39332,7 +39339,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>34.21293454407457</v>
+        <v>34.21293454407456</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>0</v>
@@ -39431,7 +39438,7 @@
         <v>137984.0624287731</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>36.00362942355253</v>
+        <v>36.00362942355252</v>
       </c>
     </row>
     <row r="218">
@@ -39462,7 +39469,7 @@
         <v>2791.119704026462</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.7282756988867258</v>
+        <v>0.7282756988867257</v>
       </c>
     </row>
     <row r="219">
@@ -39617,7 +39624,7 @@
         <v>3309.966135976186</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.8636562228026171</v>
+        <v>0.863656222802617</v>
       </c>
     </row>
     <row r="224">
@@ -39741,7 +39748,7 @@
         <v>27.75678691452548</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.007242467372454307</v>
+        <v>0.007242467372454306</v>
       </c>
     </row>
     <row r="228">
@@ -39772,7 +39779,7 @@
         <v>22094.82347531904</v>
       </c>
       <c r="G228" s="2" t="n">
-        <v>5.76511390215683</v>
+        <v>5.765113902156829</v>
       </c>
     </row>
     <row r="229">
@@ -39797,13 +39804,13 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>24.99359038000249</v>
+        <v>24.99359038000248</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>46685.27860369316</v>
+        <v>46685.2786036932</v>
       </c>
       <c r="G229" s="2" t="n">
-        <v>12.18140298811914</v>
+        <v>12.18140298811915</v>
       </c>
     </row>
     <row r="230">
@@ -39831,7 +39838,7 @@
         <v>9.255095738682277</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>9767.235609922602</v>
+        <v>9767.235609922604</v>
       </c>
       <c r="G230" s="2" t="n">
         <v>2.548525715233982</v>
@@ -39890,10 +39897,10 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>66.59251495416571</v>
+        <v>66.59251495416569</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>87.19069513370007</v>
+        <v>87.19069513370006</v>
       </c>
       <c r="G232" s="2" t="n">
         <v>0.0227503192870272</v>
@@ -39927,7 +39934,7 @@
         <v>656.2737306456557</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.171238879205889</v>
+        <v>0.1712388792058889</v>
       </c>
     </row>
     <row r="234">
@@ -39952,10 +39959,10 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.5742136338365785</v>
+        <v>0.5742136338365786</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>125.2256120123902</v>
+        <v>125.2256120123903</v>
       </c>
       <c r="G234" s="2" t="n">
         <v>0.0326746179948063</v>
@@ -39989,7 +39996,7 @@
         <v>350893.2051467203</v>
       </c>
       <c r="G235" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="236">
@@ -40265,10 +40272,10 @@
         <v>30.58695415080978</v>
       </c>
       <c r="F244" s="2" t="n">
-        <v>37.70950032372642</v>
+        <v>37.70950032372643</v>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.03948608829634373</v>
+        <v>0.03948608829634374</v>
       </c>
     </row>
     <row r="245">
@@ -40513,10 +40520,10 @@
         <v>0.5014782193202124</v>
       </c>
       <c r="F252" s="2" t="n">
-        <v>936.7061725305323</v>
+        <v>936.7061725305332</v>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.9808367206870423</v>
+        <v>0.9808367206870432</v>
       </c>
     </row>
     <row r="253">
@@ -40606,10 +40613,10 @@
         <v>30.19083516056306</v>
       </c>
       <c r="F255" s="2" t="n">
-        <v>39.52936611762219</v>
+        <v>39.5293661176222</v>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.04139169247588388</v>
+        <v>0.04139169247588389</v>
       </c>
     </row>
     <row r="256">
@@ -40758,7 +40765,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.06789314425439584</v>
+        <v>0.06789314425439583</v>
       </c>
       <c r="F260" s="2" t="n">
         <v>0</v>
@@ -41068,7 +41075,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>1.191672959031902</v>
+        <v>1.191672959031903</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>0</v>
@@ -41099,7 +41106,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.1726928023549725</v>
+        <v>0.1726928023549726</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>0</v>
@@ -41192,7 +41199,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.05532809425898656</v>
+        <v>0.05532809425898657</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>255.7444710503291</v>
@@ -41223,13 +41230,13 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.2892972898616937</v>
+        <v>0.2892972898616938</v>
       </c>
       <c r="F275" s="2" t="n">
-        <v>540.3755271308565</v>
+        <v>540.3755271308572</v>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.02604313591944823</v>
+        <v>0.02604313591944826</v>
       </c>
     </row>
     <row r="276">
@@ -41257,10 +41264,10 @@
         <v>0.1071264301728156</v>
       </c>
       <c r="F276" s="2" t="n">
-        <v>113.0543770794948</v>
+        <v>113.0543770794949</v>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.005448600761405042</v>
+        <v>0.005448600761405045</v>
       </c>
     </row>
     <row r="277">
@@ -41285,7 +41292,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.0785339140140231</v>
+        <v>0.07853391401402313</v>
       </c>
       <c r="F277" s="2" t="n">
         <v>0</v>
@@ -41347,13 +41354,13 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>4.854655696816714</v>
+        <v>4.854655696816715</v>
       </c>
       <c r="F279" s="2" t="n">
         <v>1065.068919468274</v>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.05133047897369933</v>
+        <v>0.05133047897369934</v>
       </c>
     </row>
     <row r="280">
@@ -41939,10 +41946,10 @@
         <v>0.5115909831098682</v>
       </c>
       <c r="F298" s="2" t="n">
-        <v>955.5957033180403</v>
+        <v>955.5957033180412</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.6386384040852046</v>
+        <v>0.6386384040852052</v>
       </c>
     </row>
     <row r="299">
@@ -41970,10 +41977,10 @@
         <v>0.1894415110330357</v>
       </c>
       <c r="F299" s="2" t="n">
-        <v>199.9244443064893</v>
+        <v>199.9244443064894</v>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.1336123923602695</v>
+        <v>0.1336123923602696</v>
       </c>
     </row>
     <row r="300">
@@ -42029,7 +42036,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>17.29054612440255</v>
+        <v>17.29054612440256</v>
       </c>
       <c r="F301" s="2" t="n">
         <v>22.63880162606257</v>
@@ -42404,10 +42411,10 @@
         <v>15.41570193552856</v>
       </c>
       <c r="F313" s="2" t="n">
-        <v>19.00543657475924</v>
+        <v>19.00543657475925</v>
       </c>
       <c r="G313" s="2" t="n">
-        <v>0.01755480544621397</v>
+        <v>0.01755480544621398</v>
       </c>
     </row>
     <row r="314">
@@ -42432,7 +42439,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>3.849605793315595</v>
+        <v>3.849605793315594</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>502.4408451184867</v>
@@ -42652,10 +42659,10 @@
         <v>0.5895750939735499</v>
       </c>
       <c r="F321" s="2" t="n">
-        <v>1101.261447494004</v>
+        <v>1101.261447494005</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>1.017205281242961</v>
+        <v>1.017205281242962</v>
       </c>
     </row>
     <row r="322">
@@ -42683,10 +42690,10 @@
         <v>0.2183189312502152</v>
       </c>
       <c r="F322" s="2" t="n">
-        <v>230.3998251163363</v>
+        <v>230.3998251163364</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>0.2128140592219068</v>
+        <v>0.2128140592219069</v>
       </c>
     </row>
     <row r="323">
@@ -42748,7 +42755,7 @@
         <v>20.74218540957362</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0.01915899316293267</v>
+        <v>0.01915899316293268</v>
       </c>
     </row>
     <row r="325">
@@ -42838,10 +42845,10 @@
         <v>203.2438958301459</v>
       </c>
       <c r="F327" s="2" t="n">
-        <v>5880.966860734228</v>
+        <v>5880.96686073423</v>
       </c>
       <c r="G327" s="2" t="n">
-        <v>5.432089321901247</v>
+        <v>5.43208932190125</v>
       </c>
     </row>
     <row r="328">
@@ -43117,7 +43124,7 @@
         <v>45.76085711048115</v>
       </c>
       <c r="F336" s="2" t="n">
-        <v>56.41683207531805</v>
+        <v>56.41683207531806</v>
       </c>
       <c r="G336" s="2" t="n">
         <v>0.04378800314233526</v>
@@ -43365,10 +43372,10 @@
         <v>0.4003971602235281</v>
       </c>
       <c r="F344" s="2" t="n">
-        <v>747.8978687319401</v>
+        <v>747.8978687319409</v>
       </c>
       <c r="G344" s="2" t="n">
-        <v>0.5804819771244736</v>
+        <v>0.5804819771244741</v>
       </c>
     </row>
     <row r="345">
@@ -43399,7 +43406,7 @@
         <v>156.4710528574622</v>
       </c>
       <c r="G345" s="2" t="n">
-        <v>0.1214452265781255</v>
+        <v>0.1214452265781256</v>
       </c>
     </row>
     <row r="346">
@@ -43455,10 +43462,10 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>44.513530114745</v>
+        <v>44.51353011474501</v>
       </c>
       <c r="F347" s="2" t="n">
-        <v>58.28231050037436</v>
+        <v>58.28231050037437</v>
       </c>
       <c r="G347" s="2" t="n">
         <v>0.0452358968317447</v>
@@ -43551,10 +43558,10 @@
         <v>554.774395728547</v>
       </c>
       <c r="F350" s="2" t="n">
-        <v>4006.851913040632</v>
+        <v>4006.851913040633</v>
       </c>
       <c r="G350" s="2" t="n">
-        <v>3.109923717887276</v>
+        <v>3.109923717887277</v>
       </c>
     </row>
     <row r="351">
@@ -43610,7 +43617,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.07650589172265036</v>
+        <v>0.07650589172265032</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>0</v>
@@ -44078,10 +44085,10 @@
         <v>0.3043900888894308</v>
       </c>
       <c r="F367" s="2" t="n">
-        <v>568.5672161521833</v>
+        <v>568.5672161521838</v>
       </c>
       <c r="G367" s="2" t="n">
-        <v>0.02816476637331045</v>
+        <v>0.02816476637331048</v>
       </c>
     </row>
     <row r="368">
@@ -44112,7 +44119,7 @@
         <v>118.9524862297138</v>
       </c>
       <c r="G368" s="2" t="n">
-        <v>0.005892476542804362</v>
+        <v>0.005892476542804365</v>
       </c>
     </row>
     <row r="369">
@@ -44202,10 +44209,10 @@
         <v>5.033436872084478</v>
       </c>
       <c r="F371" s="2" t="n">
-        <v>1104.291942696999</v>
+        <v>1104.291942697</v>
       </c>
       <c r="G371" s="2" t="n">
-        <v>0.0547026344298847</v>
+        <v>0.05470263442988471</v>
       </c>
     </row>
     <row r="372">
@@ -44323,7 +44330,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>0.0611841298882288</v>
+        <v>0.06118412988822879</v>
       </c>
       <c r="F375" s="2" t="n">
         <v>0</v>
@@ -44729,7 +44736,7 @@
         <v>0.006547364990315612</v>
       </c>
       <c r="F388" s="2" t="n">
-        <v>0.2928515828011956</v>
+        <v>0.2928515828011957</v>
       </c>
       <c r="G388" s="2" t="n">
         <v>1.03443561518377e-05</v>
@@ -44791,10 +44798,10 @@
         <v>0.2636981191377784</v>
       </c>
       <c r="F390" s="2" t="n">
-        <v>492.5590910326758</v>
+        <v>492.5590910326763</v>
       </c>
       <c r="G390" s="2" t="n">
-        <v>0.01739859697779528</v>
+        <v>0.0173985969777953</v>
       </c>
     </row>
     <row r="391">
@@ -44819,13 +44826,13 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>0.09764708877854067</v>
+        <v>0.09764708877854068</v>
       </c>
       <c r="F391" s="2" t="n">
-        <v>103.0504869589634</v>
+        <v>103.0504869589635</v>
       </c>
       <c r="G391" s="2" t="n">
-        <v>0.003640038167208678</v>
+        <v>0.003640038167208679</v>
       </c>
     </row>
     <row r="392">
@@ -45104,7 +45111,7 @@
         <v>0.0004710173527418762</v>
       </c>
       <c r="G400" s="2" t="n">
-        <v>4.956223472685261e-07</v>
+        <v>4.95622347268526e-07</v>
       </c>
     </row>
     <row r="401">
@@ -45135,7 +45142,7 @@
         <v>525.5246828496046</v>
       </c>
       <c r="G401" s="2" t="n">
-        <v>0.5529770301354594</v>
+        <v>0.5529770301354593</v>
       </c>
     </row>
     <row r="402">
@@ -45253,7 +45260,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>23.17402538941093</v>
+        <v>23.17402538941094</v>
       </c>
       <c r="F405" s="2" t="n">
         <v>28.57038048363179</v>
@@ -45321,7 +45328,7 @@
         <v>130.0461919363315</v>
       </c>
       <c r="G407" s="2" t="n">
-        <v>0.13683954216468</v>
+        <v>0.1368395421646799</v>
       </c>
     </row>
     <row r="408">
@@ -45442,7 +45449,7 @@
         <v>0.01240781103560979</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>0.5549785457586521</v>
+        <v>0.5549785457586522</v>
       </c>
       <c r="G411" s="2" t="n">
         <v>0.0005839695033132096</v>
@@ -45476,7 +45483,7 @@
         <v>441.7713418662933</v>
       </c>
       <c r="G412" s="2" t="n">
-        <v>0.4648485838943757</v>
+        <v>0.4648485838943756</v>
       </c>
     </row>
     <row r="413">
@@ -45504,10 +45511,10 @@
         <v>0.4997302636322939</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>933.4411835058791</v>
+        <v>933.44118350588</v>
       </c>
       <c r="G413" s="2" t="n">
-        <v>0.9822022643395573</v>
+        <v>0.982202264339558</v>
       </c>
     </row>
     <row r="414">
@@ -45600,7 +45607,7 @@
         <v>31.22877860515257</v>
       </c>
       <c r="G416" s="2" t="n">
-        <v>0.03286010688250974</v>
+        <v>0.03286010688250973</v>
       </c>
     </row>
     <row r="417">
@@ -45662,7 +45669,7 @@
         <v>461.4012734018764</v>
       </c>
       <c r="G418" s="2" t="n">
-        <v>0.4855039433790141</v>
+        <v>0.485503943379014</v>
       </c>
     </row>
     <row r="419">
@@ -45690,10 +45697,10 @@
         <v>365.4840940244388</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>4978.399396643012</v>
+        <v>4978.399396643013</v>
       </c>
       <c r="G419" s="2" t="n">
-        <v>5.238460919202259</v>
+        <v>5.23846091920226</v>
       </c>
     </row>
     <row r="420">
@@ -46217,10 +46224,10 @@
         <v>0.4993796694837204</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>932.7863121867077</v>
+        <v>932.7863121867086</v>
       </c>
       <c r="G436" s="2" t="n">
-        <v>0.9795244097535564</v>
+        <v>0.9795244097535573</v>
       </c>
     </row>
     <row r="437">
@@ -46248,7 +46255,7 @@
         <v>0.1849196766352255</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>195.1523897325025</v>
+        <v>195.1523897325026</v>
       </c>
       <c r="G437" s="2" t="n">
         <v>0.2049306758335701</v>
@@ -46307,10 +46314,10 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>20.49072752678988</v>
+        <v>20.49072752678989</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>26.82885273346012</v>
+        <v>26.82885273346013</v>
       </c>
       <c r="G439" s="2" t="n">
         <v>0.02817313654238901</v>
@@ -46403,7 +46410,7 @@
         <v>359.3880926356441</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>5090.701953038251</v>
+        <v>5090.701953038252</v>
       </c>
       <c r="G442" s="2" t="n">
         <v>5.345776155410578</v>
@@ -46679,13 +46686,13 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>12.97190838309387</v>
+        <v>12.97190838309388</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>15.99257582039032</v>
+        <v>15.99257582039033</v>
       </c>
       <c r="G451" s="2" t="n">
-        <v>0.01070656145014503</v>
+        <v>0.01070656145014504</v>
       </c>
     </row>
     <row r="452">
@@ -46741,10 +46748,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>0.9053928527032498</v>
+        <v>0.9053928527032499</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>117.0533684240192</v>
+        <v>117.0533684240193</v>
       </c>
       <c r="G453" s="2" t="n">
         <v>0.0783638043085195</v>
@@ -46927,13 +46934,13 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>0.51061989661658</v>
+        <v>0.5106198966165801</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>953.7818205265661</v>
+        <v>953.7818205265672</v>
       </c>
       <c r="G459" s="2" t="n">
-        <v>0.6385290140990963</v>
+        <v>0.638529014099097</v>
       </c>
     </row>
     <row r="460">
@@ -46961,10 +46968,10 @@
         <v>0.1890819189004418</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>199.5449537877863</v>
+        <v>199.5449537877864</v>
       </c>
       <c r="G460" s="2" t="n">
-        <v>0.1335895063927945</v>
+        <v>0.1335895063927946</v>
       </c>
     </row>
     <row r="461">
@@ -47643,10 +47650,10 @@
         <v>0.5104251220895948</v>
       </c>
       <c r="F482" s="2" t="n">
-        <v>953.4180031270265</v>
+        <v>953.4180031270274</v>
       </c>
       <c r="G482" s="2" t="n">
-        <v>0.6378277091774526</v>
+        <v>0.6378277091774532</v>
       </c>
     </row>
     <row r="483">
@@ -47674,10 +47681,10 @@
         <v>0.1890097941329595</v>
       </c>
       <c r="F483" s="2" t="n">
-        <v>199.468837925001</v>
+        <v>199.4688379250011</v>
       </c>
       <c r="G483" s="2" t="n">
-        <v>0.1334427832584583</v>
+        <v>0.1334427832584584</v>
       </c>
     </row>
     <row r="484">
@@ -47736,7 +47743,7 @@
         <v>11.90159743897301</v>
       </c>
       <c r="F485" s="2" t="n">
-        <v>15.58296085708364</v>
+        <v>15.58296085708365</v>
       </c>
       <c r="G485" s="2" t="n">
         <v>0.01042485477836246</v>
@@ -47829,10 +47836,10 @@
         <v>208.7134927359997</v>
       </c>
       <c r="F488" s="2" t="n">
-        <v>5102.860492969761</v>
+        <v>5102.860492969762</v>
       </c>
       <c r="G488" s="2" t="n">
-        <v>3.413765848565994</v>
+        <v>3.413765848565995</v>
       </c>
     </row>
     <row r="489">
@@ -48356,10 +48363,10 @@
         <v>0.5887011161295906</v>
       </c>
       <c r="F505" s="2" t="n">
-        <v>1099.628952981678</v>
+        <v>1099.628952981679</v>
       </c>
       <c r="G505" s="2" t="n">
-        <v>1.017884223490682</v>
+        <v>1.017884223490683</v>
       </c>
     </row>
     <row r="506">
@@ -48390,7 +48397,7 @@
         <v>230.0582836495036</v>
       </c>
       <c r="G506" s="2" t="n">
-        <v>0.2129561037613712</v>
+        <v>0.2129561037613713</v>
       </c>
     </row>
     <row r="507">
@@ -48542,10 +48549,10 @@
         <v>196.3396316146512</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>5864.515792874435</v>
+        <v>5864.515792874437</v>
       </c>
       <c r="G511" s="2" t="n">
-        <v>5.428556685227895</v>
+        <v>5.428556685227897</v>
       </c>
     </row>
     <row r="512">
@@ -49069,10 +49076,10 @@
         <v>0.5885258190553039</v>
       </c>
       <c r="F528" s="2" t="n">
-        <v>1099.301517322092</v>
+        <v>1099.301517322093</v>
       </c>
       <c r="G528" s="2" t="n">
-        <v>1.016673183330102</v>
+        <v>1.016673183330103</v>
       </c>
     </row>
     <row r="529">
@@ -49255,10 +49262,10 @@
         <v>193.2916309202537</v>
       </c>
       <c r="F534" s="2" t="n">
-        <v>5920.667071072055</v>
+        <v>5920.667071072056</v>
       </c>
       <c r="G534" s="2" t="n">
-        <v>5.475643709878442</v>
+        <v>5.475643709878443</v>
       </c>
     </row>
     <row r="535">
@@ -49379,7 +49386,7 @@
         <v>0.00166946645657991</v>
       </c>
       <c r="F538" s="2" t="n">
-        <v>0.0003914703408880843</v>
+        <v>0.0003914703408880844</v>
       </c>
       <c r="G538" s="2" t="n">
         <v>3.054947671642258e-07</v>
@@ -49438,13 +49445,13 @@
         </is>
       </c>
       <c r="E540" s="2" t="n">
-        <v>0.005678527051471636</v>
+        <v>0.005678527051471637</v>
       </c>
       <c r="F540" s="2" t="n">
-        <v>8.834960481174123</v>
+        <v>8.834960481174125</v>
       </c>
       <c r="G540" s="2" t="n">
-        <v>0.00689460710862139</v>
+        <v>0.006894607108621392</v>
       </c>
     </row>
     <row r="541">
@@ -49565,7 +49572,7 @@
         <v>2.708896488274346</v>
       </c>
       <c r="F544" s="2" t="n">
-        <v>353.5583418100602</v>
+        <v>353.5583418100603</v>
       </c>
       <c r="G544" s="2" t="n">
         <v>0.2759090843643571</v>
@@ -49717,10 +49724,10 @@
         </is>
       </c>
       <c r="E549" s="2" t="n">
-        <v>0.009876367725986763</v>
+        <v>0.009876367725986764</v>
       </c>
       <c r="F549" s="2" t="n">
-        <v>0.4417517467194763</v>
+        <v>0.4417517467194764</v>
       </c>
       <c r="G549" s="2" t="n">
         <v>0.0003447332605129274</v>
@@ -49779,13 +49786,13 @@
         </is>
       </c>
       <c r="E551" s="2" t="n">
-        <v>0.3977752266916501</v>
+        <v>0.3977752266916502</v>
       </c>
       <c r="F551" s="2" t="n">
-        <v>743.0003851949599</v>
+        <v>743.0003851949607</v>
       </c>
       <c r="G551" s="2" t="n">
-        <v>0.5798210131657342</v>
+        <v>0.5798210131657348</v>
       </c>
     </row>
     <row r="552">
@@ -49816,7 +49823,7 @@
         <v>155.446428456964</v>
       </c>
       <c r="G552" s="2" t="n">
-        <v>0.1213069433567812</v>
+        <v>0.1213069433567813</v>
       </c>
     </row>
     <row r="553">
@@ -49968,7 +49975,7 @@
         <v>534.0616030820629</v>
       </c>
       <c r="F557" s="2" t="n">
-        <v>3957.498709461249</v>
+        <v>3957.49870946125</v>
       </c>
       <c r="G557" s="2" t="n">
         <v>3.088344174572404</v>
@@ -50495,10 +50502,10 @@
         <v>0.39724933546879</v>
       </c>
       <c r="F574" s="2" t="n">
-        <v>742.0180782162033</v>
+        <v>742.018078216204</v>
       </c>
       <c r="G574" s="2" t="n">
-        <v>0.5777494983117941</v>
+        <v>0.5777494983117948</v>
       </c>
     </row>
     <row r="575">
@@ -50588,10 +50595,10 @@
         <v>29.96336866408524</v>
       </c>
       <c r="F577" s="2" t="n">
-        <v>39.23154042413127</v>
+        <v>39.23154042413128</v>
       </c>
       <c r="G577" s="2" t="n">
-        <v>0.03054642934378275</v>
+        <v>0.03054642934378276</v>
       </c>
     </row>
     <row r="578">
@@ -50681,7 +50688,7 @@
         <v>524.9176009988705</v>
       </c>
       <c r="F580" s="2" t="n">
-        <v>4125.952544054108</v>
+        <v>4125.952544054109</v>
       </c>
       <c r="G580" s="2" t="n">
         <v>3.21254573489107</v>
@@ -50740,7 +50747,7 @@
         </is>
       </c>
       <c r="E582" s="2" t="n">
-        <v>0.06821966035857149</v>
+        <v>0.06821966035857147</v>
       </c>
       <c r="F582" s="2" t="n">
         <v>0</v>
@@ -51081,7 +51088,7 @@
         </is>
       </c>
       <c r="E593" s="2" t="n">
-        <v>0.17145939817612</v>
+        <v>0.1714593981761201</v>
       </c>
       <c r="F593" s="2" t="n">
         <v>0</v>
@@ -51174,7 +51181,7 @@
         </is>
       </c>
       <c r="E596" s="2" t="n">
-        <v>0.05493293069839586</v>
+        <v>0.05493293069839587</v>
       </c>
       <c r="F596" s="2" t="n">
         <v>253.9178963754709</v>
@@ -51208,10 +51215,10 @@
         <v>0.2872310747017089</v>
       </c>
       <c r="F597" s="2" t="n">
-        <v>536.516064407316</v>
+        <v>536.5160644073164</v>
       </c>
       <c r="G597" s="2" t="n">
-        <v>0.02473617437200367</v>
+        <v>0.02473617437200369</v>
       </c>
     </row>
     <row r="598">
@@ -51239,10 +51246,10 @@
         <v>0.1063613132435698</v>
       </c>
       <c r="F598" s="2" t="n">
-        <v>112.2469216486611</v>
+        <v>112.2469216486612</v>
       </c>
       <c r="G598" s="2" t="n">
-        <v>0.005175165499823669</v>
+        <v>0.005175165499823672</v>
       </c>
     </row>
     <row r="599">
@@ -51329,13 +51336,13 @@
         </is>
       </c>
       <c r="E601" s="2" t="n">
-        <v>4.808063067241017</v>
+        <v>4.808063067241018</v>
       </c>
       <c r="F601" s="2" t="n">
         <v>1054.84690482161</v>
       </c>
       <c r="G601" s="2" t="n">
-        <v>0.04863391556086999</v>
+        <v>0.04863391556087</v>
       </c>
     </row>
     <row r="602">
@@ -51453,7 +51460,7 @@
         </is>
       </c>
       <c r="E605" s="2" t="n">
-        <v>0.06339190453428552</v>
+        <v>0.0633919045342855</v>
       </c>
       <c r="F605" s="2" t="n">
         <v>0</v>
@@ -51921,10 +51928,10 @@
         <v>0.3177814277938755</v>
       </c>
       <c r="F620" s="2" t="n">
-        <v>593.5807647510547</v>
+        <v>593.5807647510553</v>
       </c>
       <c r="G620" s="2" t="n">
-        <v>0.07622884464578132</v>
+        <v>0.07622884464578139</v>
       </c>
     </row>
     <row r="621">
@@ -51955,7 +51962,7 @@
         <v>124.1856824301559</v>
       </c>
       <c r="G621" s="2" t="n">
-        <v>0.01594817698846577</v>
+        <v>0.01594817698846578</v>
       </c>
     </row>
     <row r="622">
@@ -52042,13 +52049,13 @@
         </is>
       </c>
       <c r="E624" s="2" t="n">
-        <v>5.49696580718632</v>
+        <v>5.496965807186321</v>
       </c>
       <c r="F624" s="2" t="n">
         <v>1205.986129243518</v>
       </c>
       <c r="G624" s="2" t="n">
-        <v>0.1548751825366624</v>
+        <v>0.1548751825366625</v>
       </c>
     </row>
     <row r="625">
@@ -52166,7 +52173,7 @@
         </is>
       </c>
       <c r="E628" s="2" t="n">
-        <v>0.07681685944091288</v>
+        <v>0.07681685944091285</v>
       </c>
       <c r="F628" s="2" t="n">
         <v>0</v>
@@ -52476,7 +52483,7 @@
         </is>
       </c>
       <c r="E638" s="2" t="n">
-        <v>1.245737336480494</v>
+        <v>1.245737336480495</v>
       </c>
       <c r="F638" s="2" t="n">
         <v>0</v>
@@ -52634,10 +52641,10 @@
         <v>0.3024222649275404</v>
       </c>
       <c r="F643" s="2" t="n">
-        <v>564.8915373678587</v>
+        <v>564.8915373678593</v>
       </c>
       <c r="G643" s="2" t="n">
-        <v>0.02679409455391633</v>
+        <v>0.02679409455391636</v>
       </c>
     </row>
     <row r="644">
@@ -52879,7 +52886,7 @@
         </is>
       </c>
       <c r="E651" s="2" t="n">
-        <v>0.0722189967511167</v>
+        <v>0.07221899675111668</v>
       </c>
       <c r="F651" s="2" t="n">
         <v>0</v>
@@ -53347,10 +53354,10 @@
         <v>0.3315178393010324</v>
       </c>
       <c r="F666" s="2" t="n">
-        <v>619.2388710285624</v>
+        <v>619.238871028563</v>
       </c>
       <c r="G666" s="2" t="n">
-        <v>0.07896425336747653</v>
+        <v>0.07896425336747662</v>
       </c>
     </row>
     <row r="667">
@@ -53381,7 +53388,7 @@
         <v>129.5537294208196</v>
       </c>
       <c r="G667" s="2" t="n">
-        <v>0.01652046406210703</v>
+        <v>0.01652046406210704</v>
       </c>
     </row>
     <row r="668">
@@ -53468,10 +53475,10 @@
         </is>
       </c>
       <c r="E670" s="2" t="n">
-        <v>5.645160786722197</v>
+        <v>5.645160786722198</v>
       </c>
       <c r="F670" s="2" t="n">
-        <v>1238.498809149612</v>
+        <v>1238.498809149613</v>
       </c>
       <c r="G670" s="2" t="n">
         <v>0.1579311931735905</v>
@@ -53592,7 +53599,7 @@
         </is>
       </c>
       <c r="E674" s="2" t="n">
-        <v>0.06165058146562259</v>
+        <v>0.06165058146562258</v>
       </c>
       <c r="F674" s="2" t="n">
         <v>0</v>
@@ -53995,13 +54002,13 @@
         </is>
       </c>
       <c r="E687" s="2" t="n">
-        <v>0.00647407628944824</v>
+        <v>0.006474076289448241</v>
       </c>
       <c r="F687" s="2" t="n">
-        <v>0.2895735141304862</v>
+        <v>0.2895735141304863</v>
       </c>
       <c r="G687" s="2" t="n">
-        <v>9.765226410059916e-06</v>
+        <v>9.765226410059919e-06</v>
       </c>
     </row>
     <row r="688">
@@ -54060,10 +54067,10 @@
         <v>0.2607463831949429</v>
       </c>
       <c r="F689" s="2" t="n">
-        <v>487.045572856189</v>
+        <v>487.0455728561896</v>
       </c>
       <c r="G689" s="2" t="n">
-        <v>0.01642453490692813</v>
+        <v>0.01642453490692815</v>
       </c>
     </row>
     <row r="690">
@@ -54094,7 +54101,7 @@
         <v>101.8969792006296</v>
       </c>
       <c r="G690" s="2" t="n">
-        <v>0.003436250291685624</v>
+        <v>0.003436250291685625</v>
       </c>
     </row>
     <row r="691">
@@ -54305,7 +54312,7 @@
         </is>
       </c>
       <c r="E697" s="2" t="n">
-        <v>0.05475378743092834</v>
+        <v>0.05475378743092832</v>
       </c>
       <c r="F697" s="2" t="n">
         <v>0</v>
@@ -54615,7 +54622,7 @@
         </is>
       </c>
       <c r="E707" s="2" t="n">
-        <v>1.253841776412029</v>
+        <v>1.25384177641203</v>
       </c>
       <c r="F707" s="2" t="n">
         <v>0</v>
@@ -54711,7 +54718,7 @@
         <v>0.007557698040234749</v>
       </c>
       <c r="F710" s="2" t="n">
-        <v>0.3380419201755163</v>
+        <v>0.3380419201755164</v>
       </c>
       <c r="G710" s="2" t="n">
         <v>3.452039069348307e-05</v>
@@ -54773,10 +54780,10 @@
         <v>0.3043897447551809</v>
       </c>
       <c r="F712" s="2" t="n">
-        <v>568.5665733472446</v>
+        <v>568.5665733472451</v>
       </c>
       <c r="G712" s="2" t="n">
-        <v>0.05806126126904936</v>
+        <v>0.05806126126904942</v>
       </c>
     </row>
     <row r="713">
@@ -54804,7 +54811,7 @@
         <v>0.1127151476338623</v>
       </c>
       <c r="F713" s="2" t="n">
-        <v>118.9523517456221</v>
+        <v>118.9523517456222</v>
       </c>
       <c r="G713" s="2" t="n">
         <v>0.01214725574282461</v>
@@ -54894,7 +54901,7 @@
         </is>
       </c>
       <c r="E716" s="2" t="n">
-        <v>5.352968071587132</v>
+        <v>5.352968071587133</v>
       </c>
       <c r="F716" s="2" t="n">
         <v>1174.394287877493</v>
@@ -54987,7 +54994,7 @@
         </is>
       </c>
       <c r="E719" s="2" t="n">
-        <v>0.09146638765901381</v>
+        <v>0.0914663876590138</v>
       </c>
       <c r="F719" s="2" t="n">
         <v>0</v>
@@ -55235,7 +55242,7 @@
         </is>
       </c>
       <c r="E727" s="2" t="n">
-        <v>101.409691676456</v>
+        <v>101.4096916764561</v>
       </c>
       <c r="F727" s="2" t="n">
         <v>125.0241780285624</v>
@@ -55266,7 +55273,7 @@
         </is>
       </c>
       <c r="E728" s="2" t="n">
-        <v>0.8414616438103617</v>
+        <v>0.8414616438103616</v>
       </c>
       <c r="F728" s="2" t="n">
         <v>109.825452825582</v>
@@ -55303,7 +55310,7 @@
         <v>15.84586460285048</v>
       </c>
       <c r="G729" s="2" t="n">
-        <v>0.05939375803782748</v>
+        <v>0.05939375803782745</v>
       </c>
     </row>
     <row r="730">
@@ -55328,7 +55335,7 @@
         </is>
       </c>
       <c r="E730" s="2" t="n">
-        <v>0.5930393277398827</v>
+        <v>0.5930393277398828</v>
       </c>
       <c r="F730" s="2" t="n">
         <v>0</v>
@@ -55486,10 +55493,10 @@
         <v>0.1439695924928308</v>
       </c>
       <c r="F735" s="2" t="n">
-        <v>268.9193682779444</v>
+        <v>268.9193682779447</v>
       </c>
       <c r="G735" s="2" t="n">
-        <v>1.007968469471363</v>
+        <v>1.007968469471364</v>
       </c>
     </row>
     <row r="736">
@@ -55514,13 +55521,13 @@
         </is>
       </c>
       <c r="E736" s="2" t="n">
-        <v>0.05331176280484795</v>
+        <v>0.05331176280484796</v>
       </c>
       <c r="F736" s="2" t="n">
-        <v>56.26182189763016</v>
+        <v>56.26182189763018</v>
       </c>
       <c r="G736" s="2" t="n">
-        <v>0.2108815845841617</v>
+        <v>0.2108815845841618</v>
       </c>
     </row>
     <row r="737">
@@ -55576,13 +55583,13 @@
         </is>
       </c>
       <c r="E738" s="2" t="n">
-        <v>97.27164171955475</v>
+        <v>97.27164171955476</v>
       </c>
       <c r="F738" s="2" t="n">
         <v>127.3593896275224</v>
       </c>
       <c r="G738" s="2" t="n">
-        <v>0.4773707816499781</v>
+        <v>0.4773707816499782</v>
       </c>
     </row>
     <row r="739">
@@ -55672,10 +55679,10 @@
         <v>1203.610932461351</v>
       </c>
       <c r="F741" s="2" t="n">
-        <v>1597.871813785118</v>
+        <v>1597.871813785119</v>
       </c>
       <c r="G741" s="2" t="n">
-        <v>5.989172207513737</v>
+        <v>5.989172207513739</v>
       </c>
     </row>
     <row r="742">
@@ -55700,7 +55707,7 @@
         </is>
       </c>
       <c r="E742" s="2" t="n">
-        <v>0.08740908949277432</v>
+        <v>0.08740908949277436</v>
       </c>
       <c r="F742" s="2" t="n">
         <v>0</v>
@@ -55793,7 +55800,7 @@
         </is>
       </c>
       <c r="E745" s="2" t="n">
-        <v>0.0005077436691634269</v>
+        <v>0.000507743669163427</v>
       </c>
       <c r="F745" s="2" t="n">
         <v>0.0001190599466480861</v>
@@ -55824,13 +55831,13 @@
         </is>
       </c>
       <c r="E746" s="2" t="n">
-        <v>0.02380839148352916</v>
+        <v>0.02380839148352917</v>
       </c>
       <c r="F746" s="2" t="n">
-        <v>132.8378675182587</v>
+        <v>132.8378675182588</v>
       </c>
       <c r="G746" s="2" t="n">
-        <v>0.5633954693001851</v>
+        <v>0.5633954693001852</v>
       </c>
     </row>
     <row r="747">
@@ -55858,7 +55865,7 @@
         <v>0.001727040486015286</v>
       </c>
       <c r="F747" s="2" t="n">
-        <v>2.687023290551813</v>
+        <v>2.687023290551815</v>
       </c>
       <c r="G747" s="2" t="n">
         <v>0.01139627409023925</v>
@@ -55954,7 +55961,7 @@
         <v>64.09671242793146</v>
       </c>
       <c r="G750" s="2" t="n">
-        <v>0.2718486682569625</v>
+        <v>0.2718486682569624</v>
       </c>
     </row>
     <row r="751">
@@ -55979,13 +55986,13 @@
         </is>
       </c>
       <c r="E751" s="2" t="n">
-        <v>0.8103951041877216</v>
+        <v>0.8103951041877219</v>
       </c>
       <c r="F751" s="2" t="n">
-        <v>105.770726378004</v>
+        <v>105.7707263780041</v>
       </c>
       <c r="G751" s="2" t="n">
-        <v>0.4485975959962337</v>
+        <v>0.4485975959962338</v>
       </c>
     </row>
     <row r="752">
@@ -56041,7 +56048,7 @@
         </is>
       </c>
       <c r="E753" s="2" t="n">
-        <v>0.545038151559388</v>
+        <v>0.5450381515593884</v>
       </c>
       <c r="F753" s="2" t="n">
         <v>0</v>
@@ -56072,7 +56079,7 @@
         </is>
       </c>
       <c r="E754" s="2" t="n">
-        <v>0.07898489687945094</v>
+        <v>0.07898489687945098</v>
       </c>
       <c r="F754" s="2" t="n">
         <v>0</v>
@@ -56134,13 +56141,13 @@
         </is>
       </c>
       <c r="E756" s="2" t="n">
-        <v>0.003285289936407352</v>
+        <v>0.003285289936407353</v>
       </c>
       <c r="F756" s="2" t="n">
-        <v>0.1469449708792475</v>
+        <v>0.1469449708792476</v>
       </c>
       <c r="G756" s="2" t="n">
-        <v>0.0006232268883602512</v>
+        <v>0.0006232268883602513</v>
       </c>
     </row>
     <row r="757">
@@ -56165,13 +56172,13 @@
         </is>
       </c>
       <c r="E757" s="2" t="n">
-        <v>0.02530553537836409</v>
+        <v>0.0253055353783641</v>
       </c>
       <c r="F757" s="2" t="n">
-        <v>116.9704260857304</v>
+        <v>116.9704260857305</v>
       </c>
       <c r="G757" s="2" t="n">
-        <v>0.4960980579559106</v>
+        <v>0.4960980579559107</v>
       </c>
     </row>
     <row r="758">
@@ -56199,10 +56206,10 @@
         <v>0.1323165545733734</v>
       </c>
       <c r="F758" s="2" t="n">
-        <v>247.1527747802552</v>
+        <v>247.1527747802555</v>
       </c>
       <c r="G758" s="2" t="n">
-        <v>1.048230870741925</v>
+        <v>1.048230870741926</v>
       </c>
     </row>
     <row r="759">
@@ -56227,13 +56234,13 @@
         </is>
       </c>
       <c r="E759" s="2" t="n">
-        <v>0.04899665721372148</v>
+        <v>0.0489966572137215</v>
       </c>
       <c r="F759" s="2" t="n">
-        <v>51.70793567319362</v>
+        <v>51.70793567319366</v>
       </c>
       <c r="G759" s="2" t="n">
-        <v>0.219305061345843</v>
+        <v>0.2193050613458432</v>
       </c>
     </row>
     <row r="760">
@@ -56258,7 +56265,7 @@
         </is>
       </c>
       <c r="E760" s="2" t="n">
-        <v>0.03591923354852358</v>
+        <v>0.0359192335485236</v>
       </c>
       <c r="F760" s="2" t="n">
         <v>0</v>
@@ -56320,13 +56327,13 @@
         </is>
       </c>
       <c r="E762" s="2" t="n">
-        <v>2.192701511039339</v>
+        <v>2.19270151103934</v>
       </c>
       <c r="F762" s="2" t="n">
-        <v>481.0594973008015</v>
+        <v>481.0594973008018</v>
       </c>
       <c r="G762" s="2" t="n">
-        <v>2.040282235077608</v>
+        <v>2.040282235077609</v>
       </c>
     </row>
     <row r="763">
@@ -56351,10 +56358,10 @@
         </is>
       </c>
       <c r="E763" s="2" t="n">
-        <v>0.4069453132864437</v>
+        <v>0.4069453132864438</v>
       </c>
       <c r="F763" s="2" t="n">
-        <v>88.74741543732142</v>
+        <v>88.74741543732144</v>
       </c>
       <c r="G763" s="2" t="n">
         <v>0.3763978803906622</v>
@@ -56385,10 +56392,10 @@
         <v>1111.554076254756</v>
       </c>
       <c r="F764" s="2" t="n">
-        <v>1378.524242321197</v>
+        <v>1378.524242321198</v>
       </c>
       <c r="G764" s="2" t="n">
-        <v>5.846633395688023</v>
+        <v>5.846633395688026</v>
       </c>
     </row>
     <row r="765">
@@ -56444,7 +56451,7 @@
         </is>
       </c>
       <c r="E766" s="2" t="n">
-        <v>0.03458833150362734</v>
+        <v>0.03458833150362733</v>
       </c>
       <c r="F766" s="2" t="n">
         <v>0</v>
@@ -56754,7 +56761,7 @@
         </is>
       </c>
       <c r="E776" s="2" t="n">
-        <v>0.5966024133207791</v>
+        <v>0.5966024133207793</v>
       </c>
       <c r="F776" s="2" t="n">
         <v>0</v>
@@ -56912,10 +56919,10 @@
         <v>0.1448345873677133</v>
       </c>
       <c r="F781" s="2" t="n">
-        <v>270.5350835917782</v>
+        <v>270.5350835917784</v>
       </c>
       <c r="G781" s="2" t="n">
-        <v>1.007873585036166</v>
+        <v>1.007873585036167</v>
       </c>
     </row>
     <row r="782">
@@ -56943,7 +56950,7 @@
         <v>0.05363206934179562</v>
       </c>
       <c r="F782" s="2" t="n">
-        <v>56.59985291341863</v>
+        <v>56.59985291341864</v>
       </c>
       <c r="G782" s="2" t="n">
         <v>0.2108617333877675</v>
@@ -57064,10 +57071,10 @@
         </is>
       </c>
       <c r="E786" s="2" t="n">
-        <v>0.4503048618349179</v>
+        <v>0.450304861834918</v>
       </c>
       <c r="F786" s="2" t="n">
-        <v>98.20334905437122</v>
+        <v>98.20334905437123</v>
       </c>
       <c r="G786" s="2" t="n">
         <v>0.3658548095127545</v>
@@ -57157,7 +57164,7 @@
         </is>
       </c>
       <c r="E789" s="2" t="n">
-        <v>0.03584411687763459</v>
+        <v>0.03584411687763457</v>
       </c>
       <c r="F789" s="2" t="n">
         <v>0</v>
@@ -57467,7 +57474,7 @@
         </is>
       </c>
       <c r="E799" s="2" t="n">
-        <v>0.6793190280414431</v>
+        <v>0.6793190280414432</v>
       </c>
       <c r="F799" s="2" t="n">
         <v>0</v>
@@ -57625,10 +57632,10 @@
         <v>0.16491534214515</v>
       </c>
       <c r="F804" s="2" t="n">
-        <v>308.0437254917092</v>
+        <v>308.0437254917095</v>
       </c>
       <c r="G804" s="2" t="n">
-        <v>0.7444984659394135</v>
+        <v>0.7444984659394142</v>
       </c>
     </row>
     <row r="805">
@@ -57656,10 +57663,10 @@
         <v>0.06106794810689201</v>
       </c>
       <c r="F805" s="2" t="n">
-        <v>64.44720338024993</v>
+        <v>64.44720338024995</v>
       </c>
       <c r="G805" s="2" t="n">
-        <v>0.1557598486191949</v>
+        <v>0.155759848619195</v>
       </c>
     </row>
     <row r="806">
@@ -57870,7 +57877,7 @@
         </is>
       </c>
       <c r="E812" s="2" t="n">
-        <v>0.03638195121064417</v>
+        <v>0.03638195121064416</v>
       </c>
       <c r="F812" s="2" t="n">
         <v>0</v>
@@ -58180,7 +58187,7 @@
         </is>
       </c>
       <c r="E822" s="2" t="n">
-        <v>0.6887907201157234</v>
+        <v>0.6887907201157235</v>
       </c>
       <c r="F822" s="2" t="n">
         <v>0</v>
@@ -58338,10 +58345,10 @@
         <v>0.1672147438616409</v>
       </c>
       <c r="F827" s="2" t="n">
-        <v>312.3387550622538</v>
+        <v>312.3387550622541</v>
       </c>
       <c r="G827" s="2" t="n">
-        <v>0.005569415956469905</v>
+        <v>0.00556941595646991</v>
       </c>
     </row>
     <row r="828">
@@ -58369,7 +58376,7 @@
         <v>0.06191941373084818</v>
       </c>
       <c r="F828" s="2" t="n">
-        <v>65.34578569617028</v>
+        <v>65.3457856961703</v>
       </c>
       <c r="G828" s="2" t="n">
         <v>0.001165202382495811</v>
@@ -58583,7 +58590,7 @@
         </is>
       </c>
       <c r="E835" s="2" t="n">
-        <v>0.02258836314125567</v>
+        <v>0.02258836314125566</v>
       </c>
       <c r="F835" s="2" t="n">
         <v>0</v>
@@ -59051,10 +59058,10 @@
         <v>0.2545014669821169</v>
       </c>
       <c r="F850" s="2" t="n">
-        <v>475.3807560443648</v>
+        <v>475.3807560443652</v>
       </c>
       <c r="G850" s="2" t="n">
-        <v>0.02905920489499281</v>
+        <v>0.02905920489499284</v>
       </c>
     </row>
     <row r="851">
@@ -59082,10 +59089,10 @@
         <v>0.09424157981076521</v>
       </c>
       <c r="F851" s="2" t="n">
-        <v>99.45653078615533</v>
+        <v>99.45653078615535</v>
       </c>
       <c r="G851" s="2" t="n">
-        <v>0.006079606020043285</v>
+        <v>0.006079606020043287</v>
       </c>
     </row>
     <row r="852">
@@ -59296,7 +59303,7 @@
         </is>
       </c>
       <c r="E858" s="2" t="n">
-        <v>35.10619622488614</v>
+        <v>35.10619622488613</v>
       </c>
       <c r="F858" s="2" t="n">
         <v>0</v>
@@ -59761,10 +59768,10 @@
         </is>
       </c>
       <c r="E873" s="2" t="n">
-        <v>25.63941984229257</v>
+        <v>25.63941984229256</v>
       </c>
       <c r="F873" s="2" t="n">
-        <v>47891.61702562752</v>
+        <v>47891.61702562755</v>
       </c>
       <c r="G873" s="2" t="n">
         <v>12.35349351868922</v>
@@ -59798,7 +59805,7 @@
         <v>10019.61905808313</v>
       </c>
       <c r="G874" s="2" t="n">
-        <v>2.5845295436053</v>
+        <v>2.584529543605301</v>
       </c>
     </row>
     <row r="875">
@@ -59854,10 +59861,10 @@
         </is>
       </c>
       <c r="E876" s="2" t="n">
-        <v>68.31709564305582</v>
+        <v>68.31709564305581</v>
       </c>
       <c r="F876" s="2" t="n">
-        <v>89.448717513272</v>
+        <v>89.44871751327199</v>
       </c>
       <c r="G876" s="2" t="n">
         <v>0.02307301821661114</v>
@@ -59916,7 +59923,7 @@
         </is>
       </c>
       <c r="E878" s="2" t="n">
-        <v>0.5547282886596482</v>
+        <v>0.5547282886596483</v>
       </c>
       <c r="F878" s="2" t="n">
         <v>120.9762105156849</v>
@@ -59947,7 +59954,7 @@
         </is>
       </c>
       <c r="E879" s="2" t="n">
-        <v>1444.189997428684</v>
+        <v>1444.189997428683</v>
       </c>
       <c r="F879" s="2" t="n">
         <v>356618.5007222303</v>
@@ -60071,13 +60078,13 @@
         </is>
       </c>
       <c r="E883" s="2" t="n">
-        <v>9.420559567351238e-05</v>
+        <v>9.420559567351237e-05</v>
       </c>
       <c r="F883" s="2" t="n">
-        <v>2.209010939185032e-05</v>
+        <v>2.209010939185031e-05</v>
       </c>
       <c r="G883" s="2" t="n">
-        <v>4.669769877824592e-07</v>
+        <v>4.669769877824591e-07</v>
       </c>
     </row>
     <row r="884">
@@ -60133,10 +60140,10 @@
         </is>
       </c>
       <c r="E885" s="2" t="n">
-        <v>0.0003204311301515712</v>
+        <v>0.0003204311301515711</v>
       </c>
       <c r="F885" s="2" t="n">
-        <v>0.4985441376198813</v>
+        <v>0.4985441376198811</v>
       </c>
       <c r="G885" s="2" t="n">
         <v>0.01053904421805289</v>
@@ -60257,13 +60264,13 @@
         </is>
       </c>
       <c r="E889" s="2" t="n">
-        <v>0.1491975103519667</v>
+        <v>0.1491975103519666</v>
       </c>
       <c r="F889" s="2" t="n">
         <v>19.4728829951838</v>
       </c>
       <c r="G889" s="2" t="n">
-        <v>0.4116497606791399</v>
+        <v>0.4116497606791398</v>
       </c>
     </row>
     <row r="890">
@@ -60288,13 +60295,13 @@
         </is>
       </c>
       <c r="E890" s="2" t="n">
-        <v>0.02173183197100915</v>
+        <v>0.02173183197100914</v>
       </c>
       <c r="F890" s="2" t="n">
-        <v>2.80959157854669</v>
+        <v>2.809591578546689</v>
       </c>
       <c r="G890" s="2" t="n">
-        <v>0.05939375803782748</v>
+        <v>0.05939375803782746</v>
       </c>
     </row>
     <row r="891">
@@ -60350,7 +60357,7 @@
         </is>
       </c>
       <c r="E892" s="2" t="n">
-        <v>0.01523799753470729</v>
+        <v>0.01523799753470728</v>
       </c>
       <c r="F892" s="2" t="n">
         <v>0</v>
@@ -60412,7 +60419,7 @@
         </is>
       </c>
       <c r="E894" s="2" t="n">
-        <v>0.0006338077522362134</v>
+        <v>0.0006338077522362133</v>
       </c>
       <c r="F894" s="2" t="n">
         <v>0.02834905396424155</v>
@@ -60443,13 +60450,13 @@
         </is>
       </c>
       <c r="E895" s="2" t="n">
-        <v>0.00488201796728915</v>
+        <v>0.004882017967289149</v>
       </c>
       <c r="F895" s="2" t="n">
-        <v>22.56627703203013</v>
+        <v>22.56627703203012</v>
       </c>
       <c r="G895" s="2" t="n">
-        <v>0.4770430008721311</v>
+        <v>0.477043000872131</v>
       </c>
     </row>
     <row r="896">
@@ -60477,10 +60484,10 @@
         <v>0.02552689706574245</v>
       </c>
       <c r="F896" s="2" t="n">
-        <v>47.68143685172556</v>
+        <v>47.6814368517256</v>
       </c>
       <c r="G896" s="2" t="n">
-        <v>1.007968469471363</v>
+        <v>1.007968469471364</v>
       </c>
     </row>
     <row r="897">
@@ -60508,7 +60515,7 @@
         <v>0.009452578547656847</v>
       </c>
       <c r="F897" s="2" t="n">
-        <v>9.975646325340938</v>
+        <v>9.975646325340939</v>
       </c>
       <c r="G897" s="2" t="n">
         <v>0.2108815845841618</v>
@@ -60536,7 +60543,7 @@
         </is>
       </c>
       <c r="E898" s="2" t="n">
-        <v>0.00692964368993657</v>
+        <v>0.006929643689936569</v>
       </c>
       <c r="F898" s="2" t="n">
         <v>0</v>
@@ -60601,7 +60608,7 @@
         <v>0.4265956846848633</v>
       </c>
       <c r="F900" s="2" t="n">
-        <v>93.59135504399704</v>
+        <v>93.59135504399703</v>
       </c>
       <c r="G900" s="2" t="n">
         <v>1.978487670008934</v>
@@ -60629,13 +60636,13 @@
         </is>
       </c>
       <c r="E901" s="2" t="n">
-        <v>0.07930367949984807</v>
+        <v>0.07930367949984805</v>
       </c>
       <c r="F901" s="2" t="n">
         <v>17.29469872362739</v>
       </c>
       <c r="G901" s="2" t="n">
-        <v>0.3656037265955874</v>
+        <v>0.3656037265955873</v>
       </c>
     </row>
     <row r="902">
@@ -60666,7 +60673,7 @@
         <v>283.3147514588891</v>
       </c>
       <c r="G902" s="2" t="n">
-        <v>5.989172207513738</v>
+        <v>5.989172207513739</v>
       </c>
     </row>
     <row r="903">
@@ -60691,7 +60698,7 @@
         </is>
       </c>
       <c r="E903" s="2" t="n">
-        <v>0.01701526969251676</v>
+        <v>0.01701526969251677</v>
       </c>
       <c r="F903" s="2" t="n">
         <v>0</v>
@@ -60784,7 +60791,7 @@
         </is>
       </c>
       <c r="E906" s="2" t="n">
-        <v>9.883863927215361e-05</v>
+        <v>9.883863927215364e-05</v>
       </c>
       <c r="F906" s="2" t="n">
         <v>2.317650388019782e-05</v>
@@ -60815,10 +60822,10 @@
         </is>
       </c>
       <c r="E907" s="2" t="n">
-        <v>0.004634600410415624</v>
+        <v>0.004634600410415626</v>
       </c>
       <c r="F907" s="2" t="n">
-        <v>25.85854805625026</v>
+        <v>25.85854805625027</v>
       </c>
       <c r="G907" s="2" t="n">
         <v>0.5633954693001851</v>
@@ -60846,10 +60853,10 @@
         </is>
       </c>
       <c r="E908" s="2" t="n">
-        <v>0.0003361899753214396</v>
+        <v>0.0003361899753214397</v>
       </c>
       <c r="F908" s="2" t="n">
-        <v>0.5230626039479842</v>
+        <v>0.5230626039479844</v>
       </c>
       <c r="G908" s="2" t="n">
         <v>0.01139627409023925</v>
@@ -60945,7 +60952,7 @@
         <v>12.47722467644627</v>
       </c>
       <c r="G911" s="2" t="n">
-        <v>0.2718486682569625</v>
+        <v>0.2718486682569624</v>
       </c>
     </row>
     <row r="912">
@@ -60970,13 +60977,13 @@
         </is>
       </c>
       <c r="E912" s="2" t="n">
-        <v>0.1577535166567451</v>
+        <v>0.1577535166567452</v>
       </c>
       <c r="F912" s="2" t="n">
         <v>20.58959137246143</v>
       </c>
       <c r="G912" s="2" t="n">
-        <v>0.4485975959962337</v>
+        <v>0.4485975959962338</v>
       </c>
     </row>
     <row r="913">
@@ -61001,10 +61008,10 @@
         </is>
       </c>
       <c r="E913" s="2" t="n">
-        <v>0.02307417756364638</v>
+        <v>0.02307417756364639</v>
       </c>
       <c r="F913" s="2" t="n">
-        <v>2.983136214710086</v>
+        <v>2.983136214710087</v>
       </c>
       <c r="G913" s="2" t="n">
         <v>0.06499535178916314</v>
@@ -61032,7 +61039,7 @@
         </is>
       </c>
       <c r="E914" s="2" t="n">
-        <v>0.1060984755167876</v>
+        <v>0.1060984755167877</v>
       </c>
       <c r="F914" s="2" t="n">
         <v>0</v>
@@ -61063,7 +61070,7 @@
         </is>
       </c>
       <c r="E915" s="2" t="n">
-        <v>0.01537539550907438</v>
+        <v>0.01537539550907439</v>
       </c>
       <c r="F915" s="2" t="n">
         <v>0</v>
@@ -61094,7 +61101,7 @@
         </is>
       </c>
       <c r="E916" s="2" t="n">
-        <v>0.002272765968330645</v>
+        <v>0.002272765968330646</v>
       </c>
       <c r="F916" s="2" t="n">
         <v>0</v>
@@ -61125,13 +61132,13 @@
         </is>
       </c>
       <c r="E917" s="2" t="n">
-        <v>0.0006395226699015473</v>
+        <v>0.0006395226699015475</v>
       </c>
       <c r="F917" s="2" t="n">
-        <v>0.02860467171067039</v>
+        <v>0.0286046717106704</v>
       </c>
       <c r="G917" s="2" t="n">
-        <v>0.0006232268883602512</v>
+        <v>0.0006232268883602513</v>
       </c>
     </row>
     <row r="918">
@@ -61156,13 +61163,13 @@
         </is>
       </c>
       <c r="E918" s="2" t="n">
-        <v>0.004926038146318674</v>
+        <v>0.004926038146318677</v>
       </c>
       <c r="F918" s="2" t="n">
-        <v>22.76975263610116</v>
+        <v>22.76975263610117</v>
       </c>
       <c r="G918" s="2" t="n">
-        <v>0.4960980579559106</v>
+        <v>0.4960980579559108</v>
       </c>
     </row>
     <row r="919">
@@ -61187,13 +61194,13 @@
         </is>
       </c>
       <c r="E919" s="2" t="n">
-        <v>0.02575706798818299</v>
+        <v>0.025757067988183</v>
       </c>
       <c r="F919" s="2" t="n">
-        <v>48.11137082588572</v>
+        <v>48.11137082588578</v>
       </c>
       <c r="G919" s="2" t="n">
-        <v>1.048230870741925</v>
+        <v>1.048230870741926</v>
       </c>
     </row>
     <row r="920">
@@ -61218,13 +61225,13 @@
         </is>
       </c>
       <c r="E920" s="2" t="n">
-        <v>0.009537810556786373</v>
+        <v>0.009537810556786376</v>
       </c>
       <c r="F920" s="2" t="n">
         <v>10.06559473194637</v>
       </c>
       <c r="G920" s="2" t="n">
-        <v>0.219305061345843</v>
+        <v>0.2193050613458431</v>
       </c>
     </row>
     <row r="921">
@@ -61249,7 +61256,7 @@
         </is>
       </c>
       <c r="E921" s="2" t="n">
-        <v>0.006992126900339664</v>
+        <v>0.006992126900339668</v>
       </c>
       <c r="F921" s="2" t="n">
         <v>0</v>
@@ -61311,13 +61318,13 @@
         </is>
       </c>
       <c r="E923" s="2" t="n">
-        <v>0.4268367029335954</v>
+        <v>0.4268367029335956</v>
       </c>
       <c r="F923" s="2" t="n">
-        <v>93.64423233577234</v>
+        <v>93.64423233577239</v>
       </c>
       <c r="G923" s="2" t="n">
-        <v>2.040282235077608</v>
+        <v>2.040282235077609</v>
       </c>
     </row>
     <row r="924">
@@ -61342,7 +61349,7 @@
         </is>
       </c>
       <c r="E924" s="2" t="n">
-        <v>0.07921698184771687</v>
+        <v>0.07921698184771689</v>
       </c>
       <c r="F924" s="2" t="n">
         <v>17.27579153315261</v>
@@ -61376,10 +61383,10 @@
         <v>216.3778675083268</v>
       </c>
       <c r="F925" s="2" t="n">
-        <v>268.3469407687456</v>
+        <v>268.3469407687458</v>
       </c>
       <c r="G925" s="2" t="n">
-        <v>5.846633395688023</v>
+        <v>5.846633395688026</v>
       </c>
     </row>
     <row r="926">
@@ -61435,7 +61442,7 @@
         </is>
       </c>
       <c r="E927" s="2" t="n">
-        <v>0.005894487645162254</v>
+        <v>0.005894487645162251</v>
       </c>
       <c r="F927" s="2" t="n">
         <v>0</v>
@@ -61903,10 +61910,10 @@
         <v>0.02468247668268206</v>
       </c>
       <c r="F942" s="2" t="n">
-        <v>46.1041524263013</v>
+        <v>46.10415242630134</v>
       </c>
       <c r="G942" s="2" t="n">
-        <v>1.007873585036166</v>
+        <v>1.007873585036167</v>
       </c>
     </row>
     <row r="943">
@@ -61934,7 +61941,7 @@
         <v>0.009139890719693896</v>
       </c>
       <c r="F943" s="2" t="n">
-        <v>9.645655607329854</v>
+        <v>9.645655607329855</v>
       </c>
       <c r="G943" s="2" t="n">
         <v>0.2108617333877675</v>
@@ -62148,7 +62155,7 @@
         </is>
       </c>
       <c r="E950" s="2" t="n">
-        <v>0.007562503332377723</v>
+        <v>0.00756250333237772</v>
       </c>
       <c r="F950" s="2" t="n">
         <v>0</v>
@@ -62616,10 +62623,10 @@
         <v>0.03479435213289073</v>
       </c>
       <c r="F965" s="2" t="n">
-        <v>64.99202389340142</v>
+        <v>64.99202389340148</v>
       </c>
       <c r="G965" s="2" t="n">
-        <v>0.7444984659394137</v>
+        <v>0.7444984659394144</v>
       </c>
     </row>
     <row r="966">
@@ -62802,10 +62809,10 @@
         <v>247.4050163649555</v>
       </c>
       <c r="F971" s="2" t="n">
-        <v>415.1020332138395</v>
+        <v>415.1020332138396</v>
       </c>
       <c r="G971" s="2" t="n">
-        <v>4.755088523522836</v>
+        <v>4.755088523522837</v>
       </c>
     </row>
     <row r="972">
@@ -62861,7 +62868,7 @@
         </is>
       </c>
       <c r="E973" s="2" t="n">
-        <v>0.009355138395199233</v>
+        <v>0.00935513839519923</v>
       </c>
       <c r="F973" s="2" t="n">
         <v>0</v>
@@ -63171,7 +63178,7 @@
         </is>
       </c>
       <c r="E983" s="2" t="n">
-        <v>0.1771134394277981</v>
+        <v>0.1771134394277982</v>
       </c>
       <c r="F983" s="2" t="n">
         <v>0</v>
@@ -63329,10 +63336,10 @@
         <v>0.04299706361229395</v>
       </c>
       <c r="F988" s="2" t="n">
-        <v>80.31378698943297</v>
+        <v>80.31378698943305</v>
       </c>
       <c r="G988" s="2" t="n">
-        <v>0.005569415956469906</v>
+        <v>0.005569415956469912</v>
       </c>
     </row>
     <row r="989">
@@ -63360,10 +63367,10 @@
         <v>0.01592175970573592</v>
       </c>
       <c r="F989" s="2" t="n">
-        <v>16.80280601750275</v>
+        <v>16.80280601750276</v>
       </c>
       <c r="G989" s="2" t="n">
-        <v>0.001165202382495811</v>
+        <v>0.001165202382495812</v>
       </c>
     </row>
     <row r="990">
@@ -63574,7 +63581,7 @@
         </is>
       </c>
       <c r="E996" s="2" t="n">
-        <v>0.006336323251162027</v>
+        <v>0.006336323251162025</v>
       </c>
       <c r="F996" s="2" t="n">
         <v>0</v>
@@ -63884,7 +63891,7 @@
         </is>
       </c>
       <c r="E1006" s="2" t="n">
-        <v>0.294073285254732</v>
+        <v>0.2940732852547321</v>
       </c>
       <c r="F1006" s="2" t="n">
         <v>0</v>
@@ -64042,10 +64049,10 @@
         <v>0.07139089949144446</v>
       </c>
       <c r="F1011" s="2" t="n">
-        <v>133.350350303933</v>
+        <v>133.3503503039331</v>
       </c>
       <c r="G1011" s="2" t="n">
-        <v>0.02905920489499281</v>
+        <v>0.02905920489499284</v>
       </c>
     </row>
     <row r="1012">
@@ -64073,10 +64080,10 @@
         <v>0.02643596216542846</v>
       </c>
       <c r="F1012" s="2" t="n">
-        <v>27.89882226345314</v>
+        <v>27.89882226345315</v>
       </c>
       <c r="G1012" s="2" t="n">
-        <v>0.006079606020043285</v>
+        <v>0.006079606020043287</v>
       </c>
     </row>
     <row r="1013">
@@ -64854,7 +64861,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
@@ -65562,7 +65569,7 @@
         <v>283632.3099730055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>74.00704400977877</v>
+        <v>74.00704400977875</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>205.0628482296878</v>
@@ -65594,13 +65601,13 @@
         <v>27.51490091025526</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>189.7362804720336</v>
+        <v>189.7362804720337</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -65728,13 +65735,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>732.2477510848989</v>
+        <v>732.2477510848988</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>34.62754441452349</v>
+        <v>34.62754441452348</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>82680.91652541213</v>
+        <v>82680.91652541215</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>24.29977789385807</v>
@@ -65804,10 +65811,10 @@
         <v>26.80898621045401</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>64740.29869948899</v>
+        <v>64740.298699489</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.96752495993079</v>
+        <v>30.9675249599308</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>125.926270804251</v>
@@ -65938,19 +65945,19 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>544.5227874089336</v>
+        <v>544.5227874089335</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>27.89570727300268</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>78451.40751140828</v>
+        <v>78451.4075114083</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>27.11786945777961</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>144.0736904413363</v>
+        <v>144.0736904413364</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>0</v>
@@ -65982,7 +65989,7 @@
         <v>287899.2088624841</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>78.52148102582842</v>
+        <v>78.52148102582841</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>205.5032639991703</v>
@@ -66014,13 +66021,13 @@
         <v>33.44195415687567</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>78751.04416545376</v>
+        <v>78751.04416545377</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>21.47851897417159</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>111.8776895262054</v>
+        <v>111.8776895262055</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
@@ -66084,10 +66091,10 @@
         <v>32.97350318818762</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>86239.94204472346</v>
+        <v>86239.94204472347</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>24.43570182911944</v>
+        <v>24.43570182911945</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>126.6253972837623</v>
@@ -66122,7 +66129,7 @@
         <v>283632.3099730055</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>74.00704400977877</v>
+        <v>74.00704400977875</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>205.0628482296878</v>
@@ -66154,13 +66161,13 @@
         <v>27.51490091025526</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>189.7362804720336</v>
+        <v>189.7362804720337</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>0</v>
@@ -66221,7 +66228,7 @@
         <v>484.8638356007575</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>26.16628508207372</v>
+        <v>26.16628508207373</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>51638.46462285366</v>
@@ -66428,10 +66435,10 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>27.73287882213273</v>
+        <v>27.73287882213274</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>62182.09813201604</v>
@@ -66501,7 +66508,7 @@
         <v>438.6033393816223</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>24.36902394342163</v>
+        <v>24.36902394342162</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>40238.01992808915</v>
@@ -66510,7 +66517,7 @@
         <v>31.23079546012569</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>91.74125300737539</v>
+        <v>91.74125300737541</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>0</v>
@@ -66679,7 +66686,7 @@
         <v>74.15410231433196</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>43768.49215526194</v>
+        <v>43768.49215526195</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46.05486972426439</v>
@@ -66717,7 +66724,7 @@
         <v>51267.04353794219</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>53.94513027573562</v>
+        <v>53.94513027573561</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>108.2184485961106</v>
@@ -66778,7 +66785,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>471.2755006026463</v>
+        <v>471.2755006026464</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>25.77863598184343</v>
@@ -66790,7 +66797,7 @@
         <v>53.90228204661987</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>108.9178826842323</v>
+        <v>108.9178826842322</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>0</v>
@@ -66854,10 +66861,10 @@
         <v>25.33278654247475</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>50380.84713997552</v>
+        <v>50380.84713997553</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>33.72850264225581</v>
+        <v>33.72850264225582</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>107.490256569065</v>
@@ -67058,10 +67065,10 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>524.6119139259423</v>
+        <v>524.6119139259424</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>27.55697179833044</v>
+        <v>27.55697179833045</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>62028.03066388513</v>
@@ -67198,10 +67205,10 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>418.2208368844557</v>
+        <v>418.2208368844558</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>23.72790715118202</v>
+        <v>23.72790715118203</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>39775.81752369644</v>
@@ -67210,7 +67217,7 @@
         <v>30.97021392592166</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>95.10721134797389</v>
+        <v>95.10721134797386</v>
       </c>
       <c r="I67" s="2" t="n">
         <v>0</v>
@@ -67691,7 +67698,7 @@
         <v>289.6580589740433</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18.448854518734</v>
+        <v>18.44885451873401</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>14699.47497411457</v>
@@ -67700,7 +67707,7 @@
         <v>55.096839571544</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.74768168432632</v>
+        <v>50.74768168432631</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>0</v>
@@ -67732,7 +67739,7 @@
         <v>11354.75145822943</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>48.15807153571497</v>
+        <v>48.15807153571496</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>9.301815939861827</v>
@@ -67837,10 +67844,10 @@
         <v>14825.48609627951</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>55.23208163384828</v>
+        <v>55.2320816338483</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.22687781615543</v>
+        <v>50.22687781615544</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>0</v>
@@ -67980,7 +67987,7 @@
         <v>0.2794709985175882</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>57.45492380754794</v>
+        <v>57.45492380754793</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>0</v>
@@ -68076,7 +68083,7 @@
         <v>1390.809748649302</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>73.32446536771153</v>
+        <v>73.32446536771151</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>287506.3435243869</v>
@@ -68117,7 +68124,7 @@
         <v>100170.3647134389</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>25.83863373395854</v>
+        <v>25.83863373395855</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>197.9736096441405</v>
@@ -68146,13 +68153,13 @@
         <v>227.0249178925449</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>81.55114548126598</v>
+        <v>81.55114548126599</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>2124.121213370112</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>44.903160428456</v>
+        <v>44.90316042845599</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>9.356335124303396</v>
@@ -68178,16 +68185,16 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>51.35856348319775</v>
+        <v>51.35856348319774</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>18.44885451873401</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2606.328031409585</v>
+        <v>2606.328031409584</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>55.09683957154401</v>
+        <v>55.096839571544</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>50.74768168432631</v>
@@ -68213,7 +68220,7 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>237.6250009058514</v>
+        <v>237.6250009058515</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>84.99653199019589</v>
@@ -68222,7 +68229,7 @@
         <v>2210.344021135731</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>48.15807153571497</v>
+        <v>48.15807153571496</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>9.301815939861829</v>
@@ -68248,19 +68255,19 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.94523018694279</v>
+        <v>41.94523018694281</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15.0034680098041</v>
+        <v>15.00346800980411</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>2379.424527832216</v>
+        <v>2379.424527832217</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>51.84192846428503</v>
+        <v>51.84192846428504</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>56.72693932605743</v>
+        <v>56.72693932605742</v>
       </c>
       <c r="I97" s="2" t="n">
         <v>0</v>
@@ -73320,7 +73327,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="33" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -73442,16 +73449,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>130486.0827273468</v>
@@ -73460,10 +73467,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="3">
@@ -73517,7 +73524,7 @@
         <v>70.18171450297378</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>54.22965902303684</v>
+        <v>54.22965902303685</v>
       </c>
     </row>
     <row r="4">
@@ -73541,7 +73548,7 @@
         <v>1382.391803829019</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>732.2477510848989</v>
+        <v>732.2477510848988</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>340253.7952674468</v>
@@ -73550,7 +73557,7 @@
         <v>257572.8787420347</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>82680.91652541213</v>
+        <v>82680.91652541215</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>160.9039207068543</v>
@@ -73571,7 +73578,7 @@
         <v>47.58821359374465</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>36.7101495878202</v>
+        <v>36.71014958782021</v>
       </c>
     </row>
     <row r="5">
@@ -73604,7 +73611,7 @@
         <v>144318.3806210481</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>64740.29869948899</v>
+        <v>64740.298699489</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>109.0159985950846</v>
@@ -73613,7 +73620,7 @@
         <v>9.17296555448045</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>30.96752495993079</v>
+        <v>30.9675249599308</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>92229.38725905052</v>
@@ -73703,7 +73710,7 @@
         <v>1407.472127363921</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>544.5227874089336</v>
+        <v>544.5227874089335</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>289297.8286275438</v>
@@ -73712,7 +73719,7 @@
         <v>210846.4211161355</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>78451.40751140828</v>
+        <v>78451.4075114083</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>148.2062409272251</v>
@@ -73760,19 +73767,19 @@
         <v>703.9030256967155</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>366650.2530279378</v>
+        <v>366650.2530279379</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>287899.2088624841</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>78751.04416545376</v>
+        <v>78751.04416545377</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>174.1930423048099</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5.740757419289805</v>
+        <v>5.740757419289804</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>21.47851897417159</v>
@@ -73781,10 +73788,10 @@
         <v>206820.9704201069</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>159829.2826078309</v>
+        <v>159829.282607831</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>43.59175570939871</v>
+        <v>43.59175570939872</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>32.52068520742216</v>
@@ -73820,7 +73827,7 @@
         <v>266686.0457079728</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>86239.94204472346</v>
+        <v>86239.94204472347</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>170.8681408146041</v>
@@ -73829,7 +73836,7 @@
         <v>5.852466090123982</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>24.43570182911944</v>
+        <v>24.43570182911945</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>170017.5779548927</v>
@@ -73841,7 +73848,7 @@
         <v>51.82627977114904</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>50.17215779498385</v>
+        <v>50.17215779498386</v>
       </c>
     </row>
   </sheetData>
@@ -73866,7 +73873,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="33" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -73988,16 +73995,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>130486.0827273468</v>
@@ -74006,10 +74013,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="3">
@@ -74195,7 +74202,7 @@
         <v>1384.75301923389</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>108263.4417851559</v>
@@ -74225,7 +74232,7 @@
         <v>80.36793394696065</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>5.432089321901247</v>
+        <v>5.43208932190125</v>
       </c>
     </row>
     <row r="7">
@@ -74279,7 +74286,7 @@
         <v>50.79109755909926</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3.109923717887276</v>
+        <v>3.109923717887277</v>
       </c>
     </row>
     <row r="8">
@@ -74534,16 +74541,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>130486.0827273468</v>
@@ -74552,10 +74559,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="3">
@@ -74741,7 +74748,7 @@
         <v>1384.75301923389</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>108263.4417851559</v>
@@ -74771,7 +74778,7 @@
         <v>80.36793394696065</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>5.432089321901247</v>
+        <v>5.43208932190125</v>
       </c>
     </row>
     <row r="7">
@@ -74825,7 +74832,7 @@
         <v>50.79109755909926</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3.109923717887276</v>
+        <v>3.109923717887277</v>
       </c>
     </row>
     <row r="8">
@@ -74960,10 +74967,10 @@
         <v>473.7366336610443</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>95035.53569320412</v>
+        <v>95035.53569320413</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>43768.49215526194</v>
+        <v>43768.49215526195</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>51267.04353794219</v>
@@ -74975,19 +74982,19 @@
         <v>19.2867620227154</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>53.94513027573562</v>
+        <v>53.94513027573561</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>21227.86866275579</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>73807.66703044833</v>
+        <v>73807.66703044834</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>77.66323038228134</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5.238460919202259</v>
+        <v>5.23846091920226</v>
       </c>
     </row>
     <row r="11">
@@ -75011,7 +75018,7 @@
         <v>1356.88756021476</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>471.2755006026463</v>
+        <v>471.2755006026464</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>95228.49077557877</v>
@@ -75074,7 +75081,7 @@
         <v>98990.88060715928</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>50380.84713997552</v>
+        <v>50380.84713997553</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>80.73372701842085</v>
@@ -75083,7 +75090,7 @@
         <v>12.38639707258693</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>33.72850264225581</v>
+        <v>33.72850264225582</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>70481.70680449271</v>
@@ -75149,7 +75156,7 @@
         <v>52.80257792652635</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>3.413765848565994</v>
+        <v>3.413765848565995</v>
       </c>
     </row>
     <row r="14">
@@ -75203,7 +75210,7 @@
         <v>80.32566540136864</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>5.428556685227895</v>
+        <v>5.428556685227897</v>
       </c>
     </row>
     <row r="15">
@@ -75227,7 +75234,7 @@
         <v>1379.123800452247</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>524.6119139259423</v>
+        <v>524.6119139259424</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>108127.325019171</v>
@@ -75257,7 +75264,7 @@
         <v>80.28621025260472</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>5.475643709878442</v>
+        <v>5.475643709878443</v>
       </c>
     </row>
     <row r="16">
@@ -75335,7 +75342,7 @@
         <v>1344.348589149486</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>418.2208368844557</v>
+        <v>418.2208368844558</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>128432.4920029196</v>
@@ -75718,7 +75725,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="33" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
@@ -75874,7 +75881,7 @@
         <v>100</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>5.989172207513737</v>
+        <v>5.989172207513739</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>26.67934329523039</v>
@@ -75909,7 +75916,7 @@
         <v>215.4767127092888</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>23578.08586626756</v>
+        <v>23578.08586626757</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>11354.75145822943</v>
@@ -75921,7 +75928,7 @@
         <v>16.41722915571981</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>60.91161855114858</v>
+        <v>60.91161855114857</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>51.84192846428503</v>
@@ -75930,16 +75937,16 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>23578.08586626756</v>
+        <v>23578.08586626757</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>5.846633395688023</v>
+        <v>5.846633395688026</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>23.57808586626756</v>
+        <v>23.57808586626757</v>
       </c>
     </row>
     <row r="4">
@@ -75986,7 +75993,7 @@
         <v>58.86804982304396</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>55.23208163384828</v>
+        <v>55.2320816338483</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -76228,13 +76235,13 @@
         <v>100170.3647134389</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>204.3858794825046</v>
+        <v>204.3858794825045</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>4.892705907726859</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25.83863373395854</v>
+        <v>25.83863373395855</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>130517.4794756695</v>
@@ -76263,10 +76270,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
@@ -76277,6 +76284,9 @@
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="33" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -76335,6 +76345,21 @@
           <t>evitadas por TWh se substituir o carvão (t)</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TUST do RS (R$/MWh)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TUST do SOL-RS latente (R$/MWh)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fator nas linhas S38_TRA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -76356,7 +76381,7 @@
         <v>177.3075593515596</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>4730.449244779697</v>
@@ -76371,11 +76396,14 @@
         <v>100</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>55.09683957154401</v>
+        <v>55.096839571544</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1437319.985076501</v>
       </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -76397,26 +76425,29 @@
         <v>194.6624749354394</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>279.5702310927942</v>
+        <v>279.5702310927943</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4589.768548967947</v>
+        <v>4589.768548967948</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4589.768548967947</v>
+        <v>4589.768548967948</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.84192846428503</v>
+        <v>51.84192846428504</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>1437460.665772312</v>
       </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -76458,6 +76489,9 @@
       <c r="K4" s="2" t="n">
         <v>1437476.035992878</v>
       </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -76499,6 +76533,9 @@
       <c r="K5" s="2" t="n">
         <v>1433320.795931577</v>
       </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -76540,6 +76577,9 @@
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -76581,6 +76621,9 @@
       <c r="K7" s="2" t="n">
         <v>983158.4901479881</v>
       </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -76622,6 +76665,9 @@
       <c r="K8" s="2" t="n">
         <v>1435510.561344814</v>
       </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -76640,29 +76686,32 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>129.5280954716626</v>
+        <v>129.5280954716625</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>194.5398242513398</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3179.157209060338</v>
+        <v>3179.157209060337</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3179.157209060338</v>
+        <v>3179.157209060337</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>53.05545464093752</v>
+        <v>53.0554546409375</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>1437174.322968677</v>
       </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -76687,23 +76736,26 @@
         <v>284.9380967600119</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4842.918832923267</v>
+        <v>4842.918832923269</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4842.918832923267</v>
+        <v>4842.918832923269</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>55.00474605857159</v>
+        <v>55.00474605857158</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>1435510.561344814</v>
       </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -76728,23 +76780,26 @@
         <v>297.8700909572841</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>8079.382591601268</v>
+        <v>8079.382591601269</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>49.47306998789229</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8029.909521613376</v>
+        <v>8029.909521613377</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>99.38766273998064</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>70.65603205218071</v>
+        <v>70.65603205218066</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>1432274.097586136</v>
       </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -76781,11 +76836,14 @@
         <v>0.3936597996649849</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.219559872905096</v>
+        <v>0.2195598729050959</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -76810,23 +76868,26 @@
         <v>673.2375033600329</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>458891.9500542973</v>
+        <v>458891.9500542974</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>436436.9138406435</v>
+        <v>436436.9138406436</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>22455.0362136538</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4.893316653516555</v>
+        <v>4.893316653516554</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>4.685205543087244</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>981461.5301234397</v>
-      </c>
+        <v>981461.5301234396</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -76848,26 +76909,29 @@
         <v>177.3075593515596</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4769.830970226978</v>
+        <v>4769.830970226977</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4769.830970226978</v>
+        <v>4769.830970226977</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>55.42144409870077</v>
+        <v>55.42144409870079</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>2171287.950687627</v>
       </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -76892,23 +76956,26 @@
         <v>279.5702310927929</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4612.335150351955</v>
+        <v>4612.335150351956</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4612.335150351955</v>
+        <v>4612.335150351956</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>52.15123729603247</v>
+        <v>52.15123729603246</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>2171445.446507502</v>
       </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -76950,6 +77017,9 @@
       <c r="K16" s="2" t="n">
         <v>2171443.893420102</v>
       </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -76991,6 +77061,9 @@
       <c r="K17" s="2" t="n">
         <v>2167265.381595483</v>
       </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -77032,6 +77105,9 @@
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -77068,11 +77144,14 @@
         <v>3.290875891454202</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.149421758043504</v>
+        <v>3.149421758043505</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1493892.461444901</v>
       </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -77094,7 +77173,7 @@
         <v>177.3075593515596</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>4598.023205287453</v>
@@ -77109,11 +77188,14 @@
         <v>100</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>54.28420899760515</v>
+        <v>54.28420899760514</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1437224.404354695</v>
       </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -77155,6 +77237,9 @@
       <c r="K21" s="2" t="n">
         <v>1437366.398409675</v>
       </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -77196,6 +77281,9 @@
       <c r="K22" s="2" t="n">
         <v>1437376.070783581</v>
       </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -77237,6 +77325,9 @@
       <c r="K23" s="2" t="n">
         <v>1433272.13671309</v>
       </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -77278,6 +77369,9 @@
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -77319,6 +77413,9 @@
       <c r="K25" s="2" t="n">
         <v>983316.1704210173</v>
       </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -77340,26 +77437,29 @@
         <v>177.3075593515596</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>278.3733544109541</v>
+        <v>278.373354410954</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4728.172464383611</v>
+        <v>4728.17246438361</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4728.172464383611</v>
+        <v>4728.17246438361</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>55.07839678648187</v>
+        <v>55.07839678648188</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1437316.917608969</v>
       </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -77401,6 +77501,9 @@
       <c r="K27" s="2" t="n">
         <v>1437457.914321394</v>
       </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -77425,23 +77528,26 @@
         <v>269.2761053950292</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4572.218352971931</v>
+        <v>4572.21835297193</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4572.218352971931</v>
+        <v>4572.21835297193</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>55.21392019749909</v>
+        <v>55.2139201974991</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1437472.871720381</v>
       </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -77483,6 +77589,9 @@
       <c r="K29" s="2" t="n">
         <v>1433318.344017358</v>
       </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -77524,6 +77633,9 @@
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -77565,6 +77677,9 @@
       <c r="K31" s="2" t="n">
         <v>983162.0873042747</v>
       </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -77601,11 +77716,14 @@
         <v>100</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>54.72019630973454</v>
+        <v>54.72019630973455</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>1437372.719666955</v>
       </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -77624,19 +77742,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>200.7911885476696</v>
+        <v>200.7911885476695</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>285.4207155206144</v>
+        <v>285.4207155206143</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>4682.084825690672</v>
+        <v>4682.084825690671</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4682.084825690672</v>
+        <v>4682.084825690671</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>100</v>
@@ -77647,6 +77765,9 @@
       <c r="K33" s="2" t="n">
         <v>1437478.445651022</v>
       </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -77688,6 +77809,9 @@
       <c r="K34" s="2" t="n">
         <v>1437533.396526098</v>
       </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -77706,19 +77830,19 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>217.0594134364014</v>
+        <v>217.0594134364015</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>340.3107055024124</v>
+        <v>340.3107055024125</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>8809.024026403076</v>
+        <v>8809.02402640308</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>49.47306998789229</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>8759.550956415183</v>
+        <v>8759.550956415187</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>99.43838193834404</v>
@@ -77729,6 +77853,9 @@
       <c r="K35" s="2" t="n">
         <v>1433351.506450309</v>
       </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -77770,6 +77897,9 @@
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -77811,6 +77941,9 @@
       <c r="K37" s="2" t="n">
         <v>983141.9338362685</v>
       </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -77847,11 +77980,14 @@
         <v>100</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>54.91842546775168</v>
+        <v>54.91842546775169</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>1437312.053617869</v>
       </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -77893,6 +78029,9 @@
       <c r="K39" s="2" t="n">
         <v>1437755.318067601</v>
       </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -77934,6 +78073,9 @@
       <c r="K40" s="2" t="n">
         <v>1437467.35474559</v>
       </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -77955,26 +78097,29 @@
         <v>210.5633106789184</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>334.8249674625089</v>
+        <v>334.824967462509</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>8690.026307406555</v>
+        <v>8690.026307406561</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>49.47306998789229</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>8640.553237418662</v>
+        <v>8640.553237418668</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>99.43069136688659</v>
+        <v>99.43069136688658</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>69.17132070486318</v>
+        <v>69.17132070486316</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>1433315.760288035</v>
       </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -78016,6 +78161,9 @@
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -78037,19 +78185,19 @@
         <v>327.2648434119678</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>759.0722867881941</v>
+        <v>759.0722867881942</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>461644.132376004</v>
+        <v>461644.1323760041</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>436436.9138406435</v>
+        <v>436436.9138406436</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>25207.21853536047</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5.46031385812773</v>
+        <v>5.460313858127729</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>4.953396470785023</v>
@@ -78057,6 +78205,9 @@
       <c r="K43" s="2" t="n">
         <v>980361.6542194374</v>
       </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -78078,26 +78229,29 @@
         <v>177.3075593515596</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>277.0007106608479</v>
+        <v>277.0007106608477</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>4632.065900676169</v>
+        <v>4632.065900676167</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>4632.065900676169</v>
+        <v>4632.065900676167</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>100</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>55.0587127583411</v>
+        <v>55.05871275834111</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1437270.170511288</v>
       </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -78119,7 +78273,7 @@
         <v>194.6624749354394</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>277.8555102765711</v>
+        <v>277.8555102765712</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>4467.63053600369</v>
@@ -78134,11 +78288,14 @@
         <v>100</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51.81304637391818</v>
+        <v>51.81304637391819</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1437434.60587596</v>
       </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -78180,6 +78337,9 @@
       <c r="K46" s="2" t="n">
         <v>1437421.15644465</v>
       </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -78221,6 +78381,9 @@
       <c r="K47" s="2" t="n">
         <v>1433286.840310974</v>
       </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -78257,11 +78420,14 @@
         <v>0.5006475943005481</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2739124783014576</v>
+        <v>0.2739124783014575</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -78302,6 +78468,59 @@
       </c>
       <c r="K49" s="2" t="n">
         <v>982107.5076648837</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>v03 (SOL-RS com a TUST/MWh do RS)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Solar (latente)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>194.6624749354394</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>298.4910316253125</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>4939.373498913812</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>4939.373498913812</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>53.41095316510798</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1437111.060822367</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>35.16331390760318</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>20.7630386363046</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1.693553362951384</v>
       </c>
     </row>
   </sheetData>
@@ -78502,7 +78721,7 @@
         <v>53.27325134770938</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>54.24562209267129</v>
+        <v>54.24562209267128</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -78515,7 +78734,7 @@
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1.798312771643395</v>
+        <v>1.798312771643369</v>
       </c>
     </row>
     <row r="3">
@@ -78623,7 +78842,7 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>48.24394043824842</v>
+        <v>48.24394043824841</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>200.8457582982262</v>
@@ -78648,13 +78867,13 @@
         <v>48.24394043824842</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>25.98960497196683</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>48.19570689685107</v>
+        <v>48.19570689685109</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -78667,7 +78886,7 @@
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>85.43122965021121</v>
+        <v>85.43122965021122</v>
       </c>
     </row>
     <row r="5">
@@ -78702,10 +78921,10 @@
         <v>5.177005712640801</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.99256443450703</v>
+        <v>16.99256443450704</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16.51686796416401</v>
+        <v>16.51686796416402</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>17.13403017540754</v>
@@ -78721,16 +78940,16 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.631954515295221</v>
+        <v>3.631954515295199</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>55.09683957154401</v>
+        <v>55.096839571544</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>54.28420899760515</v>
+        <v>54.28420899760514</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>55.42144409870077</v>
+        <v>55.42144409870079</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -78743,7 +78962,7 @@
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>2.064065942691524</v>
+        <v>2.064065942691563</v>
       </c>
     </row>
     <row r="6">
@@ -78756,13 +78975,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4589.768548967947</v>
+        <v>4589.768548967948</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3179.157209060338</v>
+        <v>3179.157209060337</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4682.084825690672</v>
+        <v>4682.084825690671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -78775,7 +78994,7 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>32.74517223680662</v>
+        <v>32.74517223680661</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>16.41722915571981</v>
@@ -78797,16 +79016,16 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.405531202222488</v>
+        <v>3.40553120222251</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>51.84192846428503</v>
+        <v>51.84192846428504</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>50.92119669483661</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>53.05545464093752</v>
+        <v>53.0554546409375</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -78819,7 +79038,7 @@
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>4.116856778526754</v>
+        <v>4.116856778526727</v>
       </c>
     </row>
     <row r="7">
@@ -78838,7 +79057,7 @@
         <v>4446.356776400804</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4842.918832923267</v>
+        <v>4842.918832923269</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -78851,7 +79070,7 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8.669163200332466</v>
+        <v>8.669163200332507</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>16.98714333167105</v>
@@ -78911,10 +79130,10 @@
         <v>8729.638389703598</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8079.382591601268</v>
+        <v>8079.382591601269</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8809.024026403076</v>
+        <v>8809.02402640308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -78927,7 +79146,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8.358209151737634</v>
+        <v>8.358209151737666</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>25.99770574964628</v>
@@ -78958,7 +79177,7 @@
         <v>68.8600353174814</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>70.65603205218071</v>
+        <v>70.65603205218066</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -78971,7 +79190,7 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>2.595304157894086</v>
+        <v>2.595304157894024</v>
       </c>
     </row>
     <row r="9">
@@ -79107,7 +79326,7 @@
         <v>4.685205051864327</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>3.149421758043504</v>
+        <v>3.149421758043505</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>4.953396470785023</v>
@@ -79123,7 +79342,7 @@
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>38.50364483030865</v>
+        <v>38.50364483030864</v>
       </c>
     </row>
   </sheetData>
@@ -79270,7 +79489,7 @@
         <v>283632.3388369817</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>99618.19614025998</v>
+        <v>99618.19614026</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>200.8456566271434</v>
@@ -79279,7 +79498,7 @@
         <v>4.97894759983002</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>25.99296988487584</v>
+        <v>25.99296988487585</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>130486.0827273468</v>
@@ -79384,7 +79603,7 @@
         <v>1389.275279734491</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.7197997506952787</v>
+        <v>0.7197997506952788</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>1.958179535167892</v>
@@ -79393,13 +79612,13 @@
         <v>2738080.89774943</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>85499.55550314486</v>
+        <v>85499.55550314439</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>3.028054518675221</v>
+        <v>3.028054518675205</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>92.37269122039807</v>
+        <v>92.37269122039808</v>
       </c>
     </row>
     <row r="5">
@@ -79468,7 +79687,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>129.5280954716626</v>
+        <v>129.5280954716625</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>194.5398242513398</v>
@@ -79477,13 +79696,13 @@
         <v>161.7639545627511</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>32.77586968858866</v>
+        <v>32.77586968858865</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3179.157209060338</v>
+        <v>3179.157209060337</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1492.440898043235</v>
+        <v>1492.440898043234</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1686.716311017102</v>
@@ -79492,22 +79711,22 @@
         <v>16.34193523765581</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>61.19226306170617</v>
+        <v>61.19226306170618</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>53.05545464093752</v>
+        <v>53.0554546409375</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3179.157209060338</v>
+        <v>3179.157209060337</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>6.078359647484503</v>
+        <v>6.078359647484505</v>
       </c>
     </row>
     <row r="7">
@@ -79531,37 +79750,37 @@
         <v>232.8183885806438</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52.11970817936815</v>
+        <v>52.11970817936817</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4842.918832923267</v>
+        <v>4842.918832923269</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2179.083627051085</v>
+        <v>2179.083627051086</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2663.835205872182</v>
+        <v>2663.835205872183</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.996389349095</v>
+        <v>16.99638934909501</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>58.83602566760725</v>
+        <v>58.83602566760724</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>55.00474605857159</v>
+        <v>55.00474605857158</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4842.918832923267</v>
+        <v>4842.918832923269</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>5.968514200050209</v>
+        <v>5.968514200050207</v>
       </c>
     </row>
     <row r="8">
@@ -79588,28 +79807,28 @@
         <v>64.13896025346256</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8079.382591601268</v>
+        <v>8079.382591601269</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2370.811438061169</v>
+        <v>2370.81143806117</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5708.5711535401</v>
+        <v>5708.571153540098</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>27.12384639100905</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>36.86792741649937</v>
+        <v>36.86792741649936</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>70.65603205218071</v>
+        <v>70.65603205218066</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>49.47306998789229</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>8029.909521613376</v>
+        <v>8029.909521613377</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>99.38766273998064</v>
@@ -79648,7 +79867,7 @@
         <v>1437191.041907275</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3162.438270462366</v>
+        <v>3162.438270462365</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>4876.361934871326</v>
@@ -79657,7 +79876,7 @@
         <v>0.2050709142094038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.219559872905096</v>
+        <v>0.2195598729050959</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1434683.387553202</v>
@@ -79696,7 +79915,7 @@
         <v>361.3073704933416</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>458891.9500542973</v>
+        <v>458891.9500542974</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>437391.9189735723</v>
@@ -79705,7 +79924,7 @@
         <v>21500.03108072509</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>681.6197074049392</v>
+        <v>681.6197074049393</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>1.467093731499046</v>
@@ -79714,16 +79933,16 @@
         <v>4.685205543087244</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>436436.9138406435</v>
+        <v>436436.9138406436</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>22455.0362136538</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>4.893316653516555</v>
+        <v>4.893316653516554</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>95.2555135882799</v>
+        <v>95.25551358827988</v>
       </c>
     </row>
     <row r="11">
@@ -79765,7 +79984,7 @@
         <v>4.357080483305996</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>48.19570689685107</v>
+        <v>48.19570689685109</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1816.129892401362</v>
@@ -79801,10 +80020,10 @@
         <v>1368.145997778048</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>484.8638356007575</v>
+        <v>484.8638356007576</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>95312.20836435675</v>
+        <v>95312.20836435677</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>43609.50800684836</v>
@@ -79813,25 +80032,25 @@
         <v>51702.7003575084</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.43642880219534</v>
+        <v>51.43642880219535</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>19.44147413199338</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>54.24562209267129</v>
+        <v>54.24562209267128</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>21227.86866275579</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>74084.33970160095</v>
+        <v>74084.33970160098</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>77.7280696491613</v>
+        <v>77.72806964916131</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>5.059987248154401</v>
+        <v>5.0599872481544</v>
       </c>
     </row>
     <row r="13">
@@ -79903,19 +80122,19 @@
         <v>177.3075593515596</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>227.0249178925449</v>
+        <v>227.0249178925448</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>51.35856348319774</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4769.830970226978</v>
+        <v>4769.830970226977</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2126.321765460117</v>
+        <v>2126.321765460116</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>2643.509204766861</v>
@@ -79924,22 +80143,22 @@
         <v>17.13403017540754</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>58.3633850158207</v>
+        <v>58.36338501582068</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>55.42144409870077</v>
+        <v>55.42144409870079</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4769.830970226978</v>
+        <v>4769.830970226977</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>6.765365039566889</v>
+        <v>6.76536503956689</v>
       </c>
     </row>
     <row r="15">
@@ -79966,7 +80185,7 @@
         <v>41.94523018694198</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4612.335150351955</v>
+        <v>4612.335150351956</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>2206.945301203591</v>
@@ -79978,22 +80197,22 @@
         <v>16.49794805521001</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>60.61359853077018</v>
+        <v>60.61359853077016</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>52.15123729603247</v>
+        <v>52.15123729603246</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>4612.335150351955</v>
+        <v>4612.335150351956</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>6.307294085744183</v>
+        <v>6.307294085744181</v>
       </c>
     </row>
     <row r="16">
@@ -80101,7 +80320,7 @@
         <v>99.149455518789</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>5.434963178330489</v>
+        <v>5.43496317833049</v>
       </c>
     </row>
     <row r="18">
@@ -80188,7 +80407,7 @@
         <v>660681.0571923385</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21484.26302061386</v>
+        <v>21484.26302061387</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1013.261148335869</v>
@@ -80197,7 +80416,7 @@
         <v>0.9869124081608693</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3.149421758043504</v>
+        <v>3.149421758043505</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>659716.1061502029</v>
@@ -80242,16 +80461,16 @@
         <v>154214.2281706964</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>98840.53131674534</v>
+        <v>98840.53131674537</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>132.6155742424541</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7.540592465947872</v>
+        <v>7.540592465947871</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>39.05894973757664</v>
+        <v>39.05894973757665</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1201.465475807145</v>
@@ -80263,7 +80482,7 @@
         <v>99.52521522288667</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>87.21335297546615</v>
+        <v>87.21335297546614</v>
       </c>
     </row>
     <row r="21">
@@ -80287,7 +80506,7 @@
         <v>1368.145997778048</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>484.8638356007575</v>
+        <v>484.8638356007576</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>92695.07705567285</v>
@@ -80389,10 +80608,10 @@
         <v>177.3075593515596</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>227.0249178925449</v>
+        <v>227.0249178925448</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>51.35856348319774</v>
@@ -80407,13 +80626,13 @@
         <v>2496.000526516624</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16.51686796416401</v>
+        <v>16.51686796416402</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>60.54416625292762</v>
+        <v>60.5441662529276</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>54.28420899760515</v>
+        <v>54.28420899760514</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -80425,7 +80644,7 @@
         <v>100</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>3.281599618573752</v>
+        <v>3.281599618573751</v>
       </c>
     </row>
     <row r="24">
@@ -80722,19 +80941,19 @@
         <v>524.9630328007157</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>383231.6236811667</v>
+        <v>383231.6236811668</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>283631.2385587771</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>99600.38512238974</v>
+        <v>99600.38512238975</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>200.8436886164774</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4.978996387133467</v>
+        <v>4.978996387133466</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>25.98960497196683</v>
@@ -80743,13 +80962,13 @@
         <v>130486.0827273468</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>252745.5409538199</v>
+        <v>252745.54095382</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>65.95111815826922</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>91.55708758392173</v>
+        <v>91.55708758392171</v>
       </c>
     </row>
     <row r="30">
@@ -80875,19 +81094,19 @@
         <v>177.3075593515596</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>278.3733544109541</v>
+        <v>278.373354410954</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>227.0245880280503</v>
+        <v>227.0245880280502</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>51.3487663829038</v>
+        <v>51.34876638290379</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4728.172464383611</v>
+        <v>4728.17246438361</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>2123.970873701227</v>
+        <v>2123.970873701226</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>2604.201590682384</v>
@@ -80899,19 +81118,19 @@
         <v>58.87546541668807</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>55.07839678648187</v>
+        <v>55.07839678648188</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4728.172464383611</v>
+        <v>4728.17246438361</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>5.947461197073402</v>
+        <v>5.947461197073403</v>
       </c>
     </row>
     <row r="33">
@@ -80965,7 +81184,7 @@
         <v>100</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>5.797081762668681</v>
+        <v>5.797081762668683</v>
       </c>
     </row>
     <row r="34">
@@ -80992,7 +81211,7 @@
         <v>50.29297417755649</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4572.218352971931</v>
+        <v>4572.21835297193</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>2047.717360306601</v>
@@ -81004,22 +81223,22 @@
         <v>16.97966608015393</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>58.89397325479881</v>
+        <v>58.89397325479882</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>55.21392019749909</v>
+        <v>55.2139201974991</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>4572.218352971931</v>
+        <v>4572.21835297193</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5.978274331363344</v>
+        <v>5.978274331363345</v>
       </c>
     </row>
     <row r="35">
@@ -81043,7 +81262,7 @@
         <v>267.2448269547398</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>68.52746262998967</v>
+        <v>68.52746262998966</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>8726.746055994246</v>
@@ -81205,7 +81424,7 @@
         <v>1384.182101619249</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>523.9549797045572</v>
+        <v>523.9549797045571</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>383253.7117399096</v>
@@ -81373,10 +81592,10 @@
         <v>4787.810809757031</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>2167.911335719292</v>
+        <v>2167.911335719293</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2619.899474037738</v>
+        <v>2619.899474037739</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>17.00049686546561</v>
@@ -81385,7 +81604,7 @@
         <v>58.82181020434617</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>54.72019630973454</v>
+        <v>54.72019630973455</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>0</v>
@@ -81412,31 +81631,31 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>200.7911885476696</v>
+        <v>200.7911885476695</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>285.4207155206144</v>
+        <v>285.4207155206143</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>243.8339766338376</v>
+        <v>243.8339766338375</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>41.58673888677683</v>
+        <v>41.58673888677682</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4682.084825690672</v>
+        <v>4682.084825690671</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>2267.84800848866</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2414.236817202013</v>
+        <v>2414.236817202012</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>16.40415208528377</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>60.9601761067007</v>
+        <v>60.96017610670069</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>51.56328659308046</v>
@@ -81445,13 +81664,13 @@
         <v>0</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>4682.084825690672</v>
+        <v>4682.084825690671</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>5.800129548510099</v>
+        <v>5.800129548510101</v>
       </c>
     </row>
     <row r="43">
@@ -81520,31 +81739,31 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>217.0594134364014</v>
+        <v>217.0594134364015</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>340.3107055024124</v>
+        <v>340.3107055024125</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>272.7644206299634</v>
+        <v>272.7644206299635</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>67.54628487244896</v>
+        <v>67.54628487244898</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8809.024026403076</v>
+        <v>8809.02402640308</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2743.126970696495</v>
+        <v>2743.126970696496</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6065.897055706581</v>
+        <v>6065.897055706583</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25.88523923570964</v>
+        <v>25.88523923570965</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>38.63205554694905</v>
+        <v>38.63205554694904</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>68.8600353174814</v>
@@ -81553,13 +81772,13 @@
         <v>49.47306998789229</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>8759.550956415183</v>
+        <v>8759.550956415187</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>99.43838193834404</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>4.724206484635149</v>
+        <v>4.724206484635147</v>
       </c>
     </row>
     <row r="45">
@@ -81592,7 +81811,7 @@
         <v>1438089.893964701</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4070.636512011005</v>
+        <v>4070.636512011006</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>3600.491065922366</v>
@@ -81691,7 +81910,7 @@
         <v>1383.157276894925</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>525.7081094703972</v>
+        <v>525.7081094703971</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>383302.3240392271</v>
@@ -81721,7 +81940,7 @@
         <v>65.95739849623429</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>91.54545496220474</v>
+        <v>91.54545496220472</v>
       </c>
     </row>
     <row r="48">
@@ -81793,7 +82012,7 @@
         <v>1000</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2001.594686284699</v>
+        <v>2001.5946862847</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1337.013514983678</v>
@@ -81814,7 +82033,7 @@
         <v>1035.766093089371</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.965468947740226</v>
+        <v>0.9654689477402262</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>2.631313821844507</v>
@@ -81871,7 +82090,7 @@
         <v>59.12811338696049</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>54.91842546775168</v>
+        <v>54.91842546775169</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>0</v>
@@ -81904,16 +82123,16 @@
         <v>266.3958044701168</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>226.7404206118693</v>
+        <v>226.7404206118692</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>39.65538385824756</v>
+        <v>39.65538385824757</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>4250.468527840789</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>2044.103424846377</v>
+        <v>2044.103424846376</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>2206.365102994412</v>
@@ -81922,7 +82141,7 @@
         <v>15.95546347396619</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>62.67445640997235</v>
+        <v>62.67445640997234</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>51.90875049521263</v>
@@ -82009,43 +82228,43 @@
         <v>210.5633106789184</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>334.8249674625089</v>
+        <v>334.824967462509</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>266.6817699982465</v>
+        <v>266.6817699982466</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>68.14319746426246</v>
+        <v>68.14319746426247</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>8690.026307406555</v>
+        <v>8690.026307406561</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2679.020340973388</v>
+        <v>2679.020340973389</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>6011.005966433167</v>
+        <v>6011.00596643317</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25.95393758495503</v>
+        <v>25.95393758495504</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>38.52979906138327</v>
+        <v>38.52979906138324</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>69.17132070486318</v>
+        <v>69.17132070486316</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>49.47306998789229</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>8640.553237418662</v>
+        <v>8640.553237418668</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>99.43069136688659</v>
+        <v>99.43069136688658</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>4.753221355959424</v>
+        <v>4.753221355959422</v>
       </c>
     </row>
     <row r="54">
@@ -82117,22 +82336,22 @@
         <v>327.2648434119678</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>759.0722867881941</v>
+        <v>759.0722867881942</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>379.6339442490139</v>
+        <v>379.6339442490138</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>379.4383425391803</v>
+        <v>379.4383425391804</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>461644.132376004</v>
+        <v>461644.1323760041</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>438777.0682153048</v>
+        <v>438777.0682153049</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22867.06416069912</v>
+        <v>22867.06416069913</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>608.1688666692396</v>
@@ -82144,16 +82363,16 @@
         <v>4.953396470785023</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>436436.9138406435</v>
+        <v>436436.9138406436</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>25207.21853536047</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>5.46031385812773</v>
+        <v>5.460313858127729</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>94.71900728127754</v>
+        <v>94.71900728127753</v>
       </c>
     </row>
     <row r="56">
@@ -82177,7 +82396,7 @@
         <v>1382.88823603342</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>524.9705467540292</v>
+        <v>524.9705467540293</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>383228.5593191746</v>
@@ -82186,7 +82405,7 @@
         <v>283615.1640200093</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>99613.39529916525</v>
+        <v>99613.39529916526</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>200.8684095367184</v>
@@ -82207,7 +82426,7 @@
         <v>65.95084589750772</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>91.56206987562342</v>
+        <v>91.56206987562344</v>
       </c>
     </row>
     <row r="57">
@@ -82333,16 +82552,16 @@
         <v>177.3075593515596</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>277.0007106608479</v>
+        <v>277.0007106608477</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>226.3836343557619</v>
+        <v>226.3836343557618</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>50.61707630508594</v>
+        <v>50.61707630508593</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4632.065900676169</v>
+        <v>4632.065900676167</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>2081.710041645811</v>
@@ -82357,19 +82576,19 @@
         <v>59.80068431677807</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>55.0587127583411</v>
+        <v>55.05871275834111</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>4632.065900676169</v>
+        <v>4632.065900676167</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>6.003306014144886</v>
+        <v>6.003306014144889</v>
       </c>
     </row>
     <row r="60">
@@ -82387,13 +82606,13 @@
         <v>194.6624749354394</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>277.8555102765711</v>
+        <v>277.8555102765712</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>236.7649838940575</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>41.09052638251364</v>
+        <v>41.09052638251368</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>4467.63053600369</v>
@@ -82402,16 +82621,16 @@
         <v>2152.815054568769</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2314.815481434921</v>
+        <v>2314.815481434922</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>16.07897043883244</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>62.19303678703785</v>
+        <v>62.19303678703786</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>51.81304637391818</v>
+        <v>51.81304637391819</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>0</v>
@@ -82423,7 +82642,7 @@
         <v>100</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>5.861293611180956</v>
+        <v>5.861293611180959</v>
       </c>
     </row>
     <row r="61">
@@ -82501,7 +82720,7 @@
         <v>266.4824061687337</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>67.69429297278774</v>
+        <v>67.69429297278772</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>8615.396100990565</v>
@@ -82531,7 +82750,7 @@
         <v>99.42575977461784</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>4.747476679677208</v>
+        <v>4.747476679677209</v>
       </c>
     </row>
     <row r="63">
@@ -82564,7 +82783,7 @@
         <v>1437952.686261524</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3949.550150440152</v>
+        <v>3949.550150440151</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>3676.775772968203</v>
@@ -82573,7 +82792,7 @@
         <v>0.2719774230868356</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.2739124783014576</v>
+        <v>0.2739124783014575</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>1434683.387553202</v>
@@ -82672,16 +82891,16 @@
         <v>283632.3099730055</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99618.11404815708</v>
+        <v>99618.11404815713</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>200.8457582982262</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.97894507941337</v>
+        <v>4.978945079413368</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>25.99295599022124</v>
+        <v>25.99295599022125</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>130486.0827273468</v>
@@ -82690,10 +82909,10 @@
         <v>252764.3412938158</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>65.95278842531911</v>
+        <v>65.95278842531913</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>91.5571603196307</v>
+        <v>91.55716031963068</v>
       </c>
     </row>
     <row r="66">
@@ -82879,7 +83098,7 @@
         <v>1384.75301923389</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>531.4060814249979</v>
+        <v>531.406081424998</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>108263.4417851559</v>
@@ -82909,7 +83128,7 @@
         <v>80.36793394696065</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>5.432089321901247</v>
+        <v>5.43208932190125</v>
       </c>
     </row>
     <row r="70">
@@ -82963,7 +83182,7 @@
         <v>50.79109755909926</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>3.109923717887276</v>
+        <v>3.109923717887277</v>
       </c>
     </row>
     <row r="71">
@@ -83098,10 +83317,10 @@
         <v>473.7366336610443</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>95035.53569320412</v>
+        <v>95035.53569320413</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43768.49215526194</v>
+        <v>43768.49215526195</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>51267.04353794219</v>
@@ -83113,19 +83332,19 @@
         <v>19.2867620227154</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>53.94513027573562</v>
+        <v>53.94513027573561</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>21227.86866275579</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>73807.66703044833</v>
+        <v>73807.66703044834</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>77.66323038228134</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>5.238460919202259</v>
+        <v>5.23846091920226</v>
       </c>
     </row>
     <row r="74">
@@ -83149,7 +83368,7 @@
         <v>1356.88756021476</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>471.2755006026463</v>
+        <v>471.2755006026464</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>95228.49077557877</v>
@@ -83212,7 +83431,7 @@
         <v>98990.88060715928</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>50380.84713997552</v>
+        <v>50380.84713997553</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>80.73372701842085</v>
@@ -83221,7 +83440,7 @@
         <v>12.38639707258693</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>33.72850264225581</v>
+        <v>33.72850264225582</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>70481.70680449271</v>
@@ -83287,7 +83506,7 @@
         <v>52.80257792652635</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>3.413765848565994</v>
+        <v>3.413765848565995</v>
       </c>
     </row>
     <row r="77">
@@ -83341,7 +83560,7 @@
         <v>80.32566540136864</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>5.428556685227895</v>
+        <v>5.428556685227897</v>
       </c>
     </row>
     <row r="78">
@@ -83365,7 +83584,7 @@
         <v>1379.123800452247</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>524.6119139259423</v>
+        <v>524.6119139259424</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>108127.325019171</v>
@@ -83395,7 +83614,7 @@
         <v>80.28621025260472</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>5.475643709878442</v>
+        <v>5.475643709878443</v>
       </c>
     </row>
     <row r="79">
@@ -83473,7 +83692,7 @@
         <v>1344.348589149486</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>418.2208368844557</v>
+        <v>418.2208368844558</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>128432.4920029196</v>
@@ -83881,7 +84100,7 @@
         <v>100</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>5.989172207513737</v>
+        <v>5.989172207513739</v>
       </c>
     </row>
     <row r="88">
@@ -83908,7 +84127,7 @@
         <v>215.4767127092888</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>23578.08586626756</v>
+        <v>23578.08586626757</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>11354.75145822943</v>
@@ -83920,7 +84139,7 @@
         <v>16.41722915571981</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>60.91161855114858</v>
+        <v>60.91161855114857</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>51.84192846428503</v>
@@ -83929,13 +84148,13 @@
         <v>0</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>23578.08586626756</v>
+        <v>23578.08586626757</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>5.846633395688023</v>
+        <v>5.846633395688026</v>
       </c>
     </row>
     <row r="89">
@@ -83977,7 +84196,7 @@
         <v>58.86804982304396</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>55.23208163384828</v>
+        <v>55.2320816338483</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>0</v>
@@ -84187,13 +84406,13 @@
         <v>100170.3647134389</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>204.3858794825046</v>
+        <v>204.3858794825045</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>4.892705907726859</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>25.83863373395854</v>
+        <v>25.83863373395855</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>130517.4794756695</v>
@@ -84223,13 +84442,13 @@
         <v>177.3075593515596</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>278.3834813757427</v>
+        <v>278.3834813757426</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>227.0249178925449</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>51.35856348319775</v>
+        <v>51.35856348319774</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>4730.449244779697</v>
@@ -84238,16 +84457,16 @@
         <v>2124.121213370112</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2606.328031409585</v>
+        <v>2606.328031409584</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>16.99256443450703</v>
+        <v>16.99256443450704</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>58.84926927034547</v>
+        <v>58.84926927034545</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>55.09683957154401</v>
+        <v>55.096839571544</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>0</v>
@@ -84259,7 +84478,7 @@
         <v>100</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>5.989172207513738</v>
+        <v>5.989172207513739</v>
       </c>
     </row>
     <row r="95">
@@ -84277,22 +84496,22 @@
         <v>194.6624749354394</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>279.5702310927942</v>
+        <v>279.5702310927943</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>237.6250009058514</v>
+        <v>237.6250009058515</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>41.94523018694279</v>
+        <v>41.94523018694281</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>4589.768548967947</v>
+        <v>4589.768548967948</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>2210.344021135731</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2379.424527832216</v>
+        <v>2379.424527832217</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>16.41722915571981</v>
@@ -84301,19 +84520,19 @@
         <v>60.91161855114857</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>51.84192846428503</v>
+        <v>51.84192846428504</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>4589.768548967947</v>
+        <v>4589.768548967948</v>
       </c>
       <c r="O95" s="2" t="n">
         <v>100</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>5.846633395688023</v>
+        <v>5.846633395688026</v>
       </c>
     </row>
     <row r="96">
@@ -84421,7 +84640,7 @@
         <v>99.43327469272673</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>4.755088523522836</v>
+        <v>4.755088523522837</v>
       </c>
     </row>
     <row r="98">
